--- a/AAII_Financials/Quarterly/CLRB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CLRB_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/CLRB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CLRB_QTR_FIN.xlsx
@@ -656,140 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -880,8 +887,14 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -972,8 +985,14 @@
       <c r="AF9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1064,8 +1083,14 @@
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,100 +1123,108 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E12" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F12" s="3">
         <v>7300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>6300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>6700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>5500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>5400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>4500</v>
-      </c>
-      <c r="J12" s="3">
-        <v>3900</v>
-      </c>
-      <c r="K12" s="3">
-        <v>4400</v>
       </c>
       <c r="L12" s="3">
         <v>3900</v>
       </c>
       <c r="M12" s="3">
+        <v>4400</v>
+      </c>
+      <c r="N12" s="3">
+        <v>3900</v>
+      </c>
+      <c r="O12" s="3">
         <v>4600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>4600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>2400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>2700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>2500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>2600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>2200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>2700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>1800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>2300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>1000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>2000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>1700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>2100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>3100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>2300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>2200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>1900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>1400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,77 +1315,83 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-200</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="3">
         <v>1700</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1368,14 +1407,20 @@
       <c r="AD14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,100 +1548,108 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>12500</v>
+      </c>
+      <c r="F17" s="3">
         <v>9400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>8300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>8700</v>
-      </c>
-      <c r="G17" s="3">
-        <v>7400</v>
-      </c>
-      <c r="H17" s="3">
-        <v>7800</v>
       </c>
       <c r="I17" s="3">
         <v>7400</v>
       </c>
       <c r="J17" s="3">
+        <v>7800</v>
+      </c>
+      <c r="K17" s="3">
+        <v>7400</v>
+      </c>
+      <c r="L17" s="3">
         <v>6100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>5900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>5800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>6000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>6400</v>
-      </c>
-      <c r="O17" s="3">
-        <v>3600</v>
-      </c>
-      <c r="P17" s="3">
-        <v>3900</v>
       </c>
       <c r="Q17" s="3">
         <v>3600</v>
       </c>
       <c r="R17" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="S17" s="3">
-        <v>3400</v>
+        <v>3600</v>
       </c>
       <c r="T17" s="3">
         <v>4000</v>
       </c>
       <c r="U17" s="3">
+        <v>3400</v>
+      </c>
+      <c r="V17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="W17" s="3">
         <v>3200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>3600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>3100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>2900</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>3500</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>4100</v>
       </c>
       <c r="AB17" s="3">
         <v>3500</v>
       </c>
       <c r="AC17" s="3">
+        <v>4100</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AE17" s="3">
         <v>3200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>2800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>2600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1598,91 +1657,97 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="G18" s="3">
         <v>-8300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-8700</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-7800</v>
       </c>
       <c r="I18" s="3">
         <v>-7400</v>
       </c>
       <c r="J18" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="L18" s="3">
         <v>-6100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-5900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-5800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-6000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-6400</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-3900</v>
       </c>
       <c r="Q18" s="3">
         <v>-3600</v>
       </c>
       <c r="R18" s="3">
-        <v>-4000</v>
+        <v>-3900</v>
       </c>
       <c r="S18" s="3">
-        <v>-3400</v>
+        <v>-3600</v>
       </c>
       <c r="T18" s="3">
         <v>-4000</v>
       </c>
       <c r="U18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="V18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="W18" s="3">
         <v>-3200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-3600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-3900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-2900</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-4100</v>
       </c>
       <c r="AB18" s="3">
         <v>-3500</v>
       </c>
       <c r="AC18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1780,10 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1724,19 +1791,19 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>5000</v>
       </c>
       <c r="F20" s="3">
-        <v>100</v>
+        <v>-4300</v>
       </c>
       <c r="G20" s="3">
         <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1769,26 +1836,26 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
@@ -1796,19 +1863,25 @@
         <v>0</v>
       </c>
       <c r="AC20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE20" s="3">
         <v>100</v>
       </c>
       <c r="AF20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH20" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1816,40 +1889,40 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="G21" s="3">
         <v>-8200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-8500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-7200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-7800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-7400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-6100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-5900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-5800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-6000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-6300</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-3900</v>
       </c>
       <c r="Q21" s="3">
         <v>-3600</v>
@@ -1858,49 +1931,55 @@
         <v>-3900</v>
       </c>
       <c r="S21" s="3">
-        <v>-3300</v>
+        <v>-3600</v>
       </c>
       <c r="T21" s="3">
         <v>-3900</v>
       </c>
       <c r="U21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="V21" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="W21" s="3">
         <v>-3200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-3600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-3800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1991,121 +2070,133 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-13700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-8200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-8600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-7300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-7800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-7400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-6100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-5900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-5800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-6000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-6400</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-3900</v>
       </c>
       <c r="Q23" s="3">
         <v>-3600</v>
       </c>
       <c r="R23" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="S23" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="T23" s="3">
         <v>-4000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-3400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-3900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-3200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-3600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-3800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-2900</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-4100</v>
       </c>
       <c r="AB23" s="3">
         <v>-3500</v>
       </c>
       <c r="AC23" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>4</v>
+      <c r="E24" s="3">
+        <v>-100</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2118,11 +2209,11 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -2175,8 +2266,14 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2364,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-13700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-8200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-8600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-7200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-7800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-7400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-6100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-5900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-5800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-6000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-6400</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-3900</v>
       </c>
       <c r="Q26" s="3">
         <v>-3600</v>
       </c>
       <c r="R26" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="S26" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="T26" s="3">
         <v>-4000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-3400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-3900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-3200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-3600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-3800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-2900</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-4100</v>
       </c>
       <c r="AB26" s="3">
         <v>-3500</v>
       </c>
       <c r="AC26" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="AE26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-13700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-8200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-8600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-7200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-7800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-7400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-6100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-5900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-5800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-6000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-6400</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-3900</v>
       </c>
       <c r="Q27" s="3">
         <v>-3600</v>
       </c>
       <c r="R27" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="S27" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="T27" s="3">
         <v>-4000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-3400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-3900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-3200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-3600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-3800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-2900</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>-5500</v>
       </c>
       <c r="AB27" s="3">
         <v>-3500</v>
       </c>
       <c r="AC27" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2952,14 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2828,19 +2967,19 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
+        <v>-5000</v>
       </c>
       <c r="F32" s="3">
-        <v>-100</v>
+        <v>4300</v>
       </c>
       <c r="G32" s="3">
         <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -2873,26 +3012,26 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
@@ -2900,111 +3039,123 @@
         <v>0</v>
       </c>
       <c r="AC32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE32" s="3">
         <v>-100</v>
       </c>
       <c r="AF32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-13700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-8200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-8600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-7200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-7800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-7400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-6100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-5900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-5800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-6000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-6400</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-3900</v>
       </c>
       <c r="Q33" s="3">
         <v>-3600</v>
       </c>
       <c r="R33" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="S33" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="T33" s="3">
         <v>-4000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-3400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-3900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-3200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-3600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-3800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-2900</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>-5500</v>
       </c>
       <c r="AB33" s="3">
         <v>-3500</v>
       </c>
       <c r="AC33" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="AD33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3246,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-13700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-8200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-8600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-7200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-7800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-7400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-6100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-5900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-5800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-6000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-6400</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-3900</v>
       </c>
       <c r="Q35" s="3">
         <v>-3600</v>
       </c>
       <c r="R35" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="S35" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="T35" s="3">
         <v>-4000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-3400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-3900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-3200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-3600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-3800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-2900</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>-5500</v>
       </c>
       <c r="AB35" s="3">
         <v>-3500</v>
       </c>
       <c r="AC35" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="AD35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3523,108 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>9600</v>
+      </c>
+      <c r="F41" s="3">
         <v>19000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>5200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>12700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>19900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>17800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>24800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>30600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>35700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>40300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>46800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>53600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>57200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>18800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>22500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>7100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>10600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>13300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>16800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>10500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>13300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>16400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>4200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>6800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>10000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>5700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>8300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>11200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>11400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,8 +3715,14 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3628,8 +3813,14 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,192 +3911,210 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>900</v>
+      </c>
+      <c r="F45" s="3">
         <v>1100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>1000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>10500</v>
+      </c>
+      <c r="F46" s="3">
         <v>20100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>5600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>13800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>20500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>18800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>25300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>31400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>36600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>41400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>47100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>54400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>57900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>19800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>23000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>7900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>11400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>14800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>18200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>11100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>14000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>17100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>5000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>7600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>10500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>6700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>9300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>12200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>12200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3996,28 +4205,34 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F48" s="3">
         <v>1400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1000</v>
-      </c>
-      <c r="H48" s="3">
-        <v>500</v>
-      </c>
-      <c r="I48" s="3">
-        <v>500</v>
       </c>
       <c r="J48" s="3">
         <v>500</v>
@@ -4032,40 +4247,40 @@
         <v>500</v>
       </c>
       <c r="N48" s="3">
+        <v>500</v>
+      </c>
+      <c r="O48" s="3">
+        <v>500</v>
+      </c>
+      <c r="P48" s="3">
         <v>600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>600</v>
-      </c>
-      <c r="P48" s="3">
-        <v>700</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>700</v>
       </c>
       <c r="R48" s="3">
         <v>700</v>
       </c>
       <c r="S48" s="3">
+        <v>700</v>
+      </c>
+      <c r="T48" s="3">
+        <v>700</v>
+      </c>
+      <c r="U48" s="3">
         <v>800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>500</v>
-      </c>
-      <c r="X48" s="3">
-        <v>200</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>200</v>
       </c>
       <c r="Z48" s="3">
         <v>200</v>
@@ -4074,22 +4289,28 @@
         <v>200</v>
       </c>
       <c r="AB48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD48" s="3">
         <v>1500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>1600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>1400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>1400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4154,10 +4375,10 @@
         <v>0</v>
       </c>
       <c r="X49" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="Y49" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="Z49" s="3">
         <v>1700</v>
@@ -4180,8 +4401,14 @@
       <c r="AF49" s="3">
         <v>1700</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4597,14 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4376,10 +4615,10 @@
         <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
@@ -4406,13 +4645,13 @@
         <v>100</v>
       </c>
       <c r="P52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q52" s="3">
         <v>100</v>
       </c>
       <c r="R52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S52" s="3">
         <v>100</v>
@@ -4424,29 +4663,29 @@
         <v>100</v>
       </c>
       <c r="V52" s="3">
+        <v>100</v>
+      </c>
+      <c r="W52" s="3">
+        <v>100</v>
+      </c>
+      <c r="X52" s="3">
         <v>500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>100</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="3">
         <v>500</v>
       </c>
-      <c r="AB52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>0</v>
-      </c>
       <c r="AD52" s="3">
         <v>0</v>
       </c>
@@ -4456,8 +4695,14 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>12100</v>
+      </c>
+      <c r="F54" s="3">
         <v>21600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>6500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>14800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>21600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>19300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>25900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>32000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>37200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>42000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>47700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>55100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>58700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>20700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>23900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>8700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>12300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>15700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>19100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>12500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>15100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>19500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>7000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>9600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>12900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>9900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>12600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>15300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>15300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>9300</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,100 +4967,108 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>9200</v>
+      </c>
+      <c r="F57" s="3">
         <v>7800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>6400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>6900</v>
-      </c>
-      <c r="G57" s="3">
-        <v>5500</v>
-      </c>
-      <c r="H57" s="3">
-        <v>6400</v>
       </c>
       <c r="I57" s="3">
         <v>5500</v>
       </c>
       <c r="J57" s="3">
+        <v>6400</v>
+      </c>
+      <c r="K57" s="3">
+        <v>5500</v>
+      </c>
+      <c r="L57" s="3">
         <v>4500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3000</v>
-      </c>
-      <c r="M57" s="3">
-        <v>3400</v>
-      </c>
-      <c r="N57" s="3">
-        <v>4900</v>
       </c>
       <c r="O57" s="3">
         <v>3400</v>
       </c>
       <c r="P57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="R57" s="3">
         <v>3800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>3200</v>
-      </c>
-      <c r="R57" s="3">
-        <v>2900</v>
-      </c>
-      <c r="S57" s="3">
-        <v>2700</v>
       </c>
       <c r="T57" s="3">
         <v>2900</v>
       </c>
       <c r="U57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="V57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="W57" s="3">
         <v>2500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>2100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>2600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>2100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>1900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>1900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>2000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>1500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>1200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>1400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4887,24 +5154,30 @@
         <v>0</v>
       </c>
       <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3">
         <v>100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F59" s="3">
         <v>8700</v>
-      </c>
-      <c r="E59" s="3">
-        <v>100</v>
-      </c>
-      <c r="F59" s="3">
-        <v>100</v>
       </c>
       <c r="G59" s="3">
         <v>100</v>
@@ -4961,22 +5234,22 @@
         <v>100</v>
       </c>
       <c r="Y59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA59" s="3">
         <v>200</v>
       </c>
       <c r="AB59" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC59" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD59" s="3">
         <v>100</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>100</v>
-      </c>
-      <c r="AD59" s="3">
-        <v>200</v>
       </c>
       <c r="AE59" s="3">
         <v>100</v>
@@ -4984,91 +5257,97 @@
       <c r="AF59" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH59" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>12900</v>
+      </c>
+      <c r="F60" s="3">
         <v>16500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>7000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>5500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>6500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>5600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>4700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>4000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>3500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>5000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>3600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>4000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>3300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>3100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>2800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>3000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>2700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>2200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>2700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>2300</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>2100</v>
-      </c>
-      <c r="AA60" s="3">
-        <v>2100</v>
       </c>
       <c r="AB60" s="3">
         <v>2100</v>
       </c>
       <c r="AC60" s="3">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="AD60" s="3">
-        <v>1400</v>
+        <v>2100</v>
       </c>
       <c r="AE60" s="3">
         <v>1600</v>
@@ -5076,8 +5355,14 @@
       <c r="AF60" s="3">
         <v>1400</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AH60" s="3">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5118,17 +5403,17 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>200</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -5168,8 +5453,14 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5183,40 +5474,40 @@
         <v>500</v>
       </c>
       <c r="G62" s="3">
+        <v>500</v>
+      </c>
+      <c r="H62" s="3">
+        <v>500</v>
+      </c>
+      <c r="I62" s="3">
         <v>600</v>
-      </c>
-      <c r="H62" s="3">
-        <v>100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>100</v>
       </c>
       <c r="J62" s="3">
         <v>100</v>
       </c>
       <c r="K62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M62" s="3">
         <v>200</v>
       </c>
       <c r="N62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P62" s="3">
         <v>300</v>
       </c>
       <c r="Q62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="R62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="S62" s="3">
         <v>400</v>
@@ -5225,31 +5516,31 @@
         <v>400</v>
       </c>
       <c r="U62" s="3">
+        <v>400</v>
+      </c>
+      <c r="V62" s="3">
+        <v>400</v>
+      </c>
+      <c r="W62" s="3">
         <v>500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>200</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>100</v>
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD62" s="3">
         <v>100</v>
@@ -5260,8 +5551,14 @@
       <c r="AF62" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH62" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,58 +5845,64 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F66" s="3">
         <v>17000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>7000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>7500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>6100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>6600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>5700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>3800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>5300</v>
-      </c>
-      <c r="O66" s="3">
-        <v>3900</v>
-      </c>
-      <c r="P66" s="3">
-        <v>4500</v>
       </c>
       <c r="Q66" s="3">
         <v>3900</v>
       </c>
       <c r="R66" s="3">
-        <v>3400</v>
+        <v>4500</v>
       </c>
       <c r="S66" s="3">
-        <v>3200</v>
+        <v>3900</v>
       </c>
       <c r="T66" s="3">
         <v>3400</v>
@@ -5596,40 +5911,46 @@
         <v>3200</v>
       </c>
       <c r="V66" s="3">
-        <v>2700</v>
+        <v>3400</v>
       </c>
       <c r="W66" s="3">
-        <v>1800</v>
+        <v>3200</v>
       </c>
       <c r="X66" s="3">
         <v>2700</v>
       </c>
       <c r="Y66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Z66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AA66" s="3">
         <v>2300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>2100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>2100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>2300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>1800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,19 +6175,25 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E70" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F70" s="3">
         <v>19300</v>
-      </c>
-      <c r="E70" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F70" s="3">
-        <v>1400</v>
       </c>
       <c r="G70" s="3">
         <v>1400</v>
@@ -5879,19 +6214,19 @@
         <v>1400</v>
       </c>
       <c r="M70" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N70" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O70" s="3">
         <v>8600</v>
       </c>
-      <c r="N70" s="3">
+      <c r="P70" s="3">
         <v>11700</v>
       </c>
-      <c r="O70" s="3">
+      <c r="Q70" s="3">
         <v>20000</v>
-      </c>
-      <c r="P70" s="3">
-        <v>1100</v>
-      </c>
-      <c r="Q70" s="3">
-        <v>1100</v>
       </c>
       <c r="R70" s="3">
         <v>1100</v>
@@ -5906,40 +6241,46 @@
         <v>1100</v>
       </c>
       <c r="V70" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W70" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X70" s="3">
         <v>1800</v>
       </c>
-      <c r="W70" s="3">
+      <c r="Y70" s="3">
         <v>2500</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Z70" s="3">
         <v>3500</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
         <v>600</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AC70" s="3">
         <v>1000</v>
       </c>
-      <c r="AB70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC70" s="3">
-        <v>0</v>
-      </c>
       <c r="AD70" s="3">
         <v>0</v>
       </c>
       <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
         <v>900</v>
       </c>
-      <c r="AF70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-239100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-217500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-210000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-196300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-188100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-179500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-172300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-164500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-157000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-150900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-145000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-139200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-133100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-126800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-123200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-119300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-115600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-111700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-108300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-104400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-101200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-97600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-93800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-90700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-87800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-84300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-80300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-76800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-73700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-70800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-68200</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="F76" s="3">
         <v>-14700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-1800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>6000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>14100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>11400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>18800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>25800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>31700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>37200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>35300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>38000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>34800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>15100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>18800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>4100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>7900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>11100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>14800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>8100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>10700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>13400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>4700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>6800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>9800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>7600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>10900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>13700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>12700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6959,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-13700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-8200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-8600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-7200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-7800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-7400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-6100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-5900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-5800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-6000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-6400</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-3900</v>
       </c>
       <c r="Q81" s="3">
         <v>-3600</v>
       </c>
       <c r="R81" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="S81" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="T81" s="3">
         <v>-4000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-3400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-3900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-3200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-3600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-3800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-2900</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>-5500</v>
       </c>
       <c r="AB81" s="3">
         <v>-3500</v>
       </c>
       <c r="AC81" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="AD81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,16 +7200,18 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -6880,13 +7277,13 @@
         <v>0</v>
       </c>
       <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3">
         <v>1300</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>100</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>100</v>
       </c>
       <c r="AD83" s="3">
         <v>100</v>
@@ -6897,8 +7294,14 @@
       <c r="AF83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,58 +7784,64 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="F89" s="3">
         <v>-8100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-7500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-7200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-7400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-7000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-5800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-5000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-4500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-6400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-6900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-4800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-3900</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-3000</v>
       </c>
       <c r="R89" s="3">
         <v>-3500</v>
       </c>
       <c r="S89" s="3">
-        <v>-2700</v>
+        <v>-3000</v>
       </c>
       <c r="T89" s="3">
         <v>-3500</v>
@@ -7417,40 +7850,46 @@
         <v>-2700</v>
       </c>
       <c r="V89" s="3">
-        <v>-2800</v>
+        <v>-3500</v>
       </c>
       <c r="W89" s="3">
         <v>-2700</v>
       </c>
       <c r="X89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="Y89" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,22 +7922,24 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -7515,17 +7956,17 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="M91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -7546,14 +7987,14 @@
         <v>0</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-400</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
@@ -7564,19 +8005,25 @@
         <v>0</v>
       </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-100</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,22 +8212,28 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-600</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H94" s="3">
         <v>0</v>
@@ -7791,17 +8250,17 @@
       <c r="L94" s="3">
         <v>0</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="M94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
@@ -7822,14 +8281,14 @@
         <v>0</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-400</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
@@ -7840,19 +8299,25 @@
         <v>0</v>
       </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-100</v>
       </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,29 +8738,35 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>43800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>400</v>
+      </c>
+      <c r="F100" s="3">
         <v>22500</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>9600</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
@@ -8289,64 +8780,70 @@
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>1200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>42200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>18400</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>9000</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>15100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-100</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>7200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-100</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>2800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>8200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,96 +8934,108 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="F102" s="3">
         <v>13800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-7500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-7200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>2100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-7000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-5800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-5100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-4600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-6400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-6800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-3500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>38300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>15400</v>
-      </c>
-      <c r="R102" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="S102" s="3">
-        <v>-2700</v>
       </c>
       <c r="T102" s="3">
         <v>-3500</v>
       </c>
       <c r="U102" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="V102" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="W102" s="3">
         <v>6400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-2800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-3100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>12200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>4300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>5800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-2300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CLRB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CLRB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
   <si>
     <t>CLRB</t>
   </si>
@@ -656,170 +656,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -893,8 +901,14 @@
       <c r="AH8" s="3">
         <v>0</v>
       </c>
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -991,8 +1005,14 @@
       <c r="AH9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1089,8 +1109,14 @@
       <c r="AH10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,106 +1151,114 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>7400</v>
+        <v>5500</v>
       </c>
       <c r="E12" s="3">
-        <v>7900</v>
+        <v>7300</v>
       </c>
       <c r="F12" s="3">
-        <v>7300</v>
+        <v>7100</v>
       </c>
       <c r="G12" s="3">
-        <v>6300</v>
+        <v>7000</v>
       </c>
       <c r="H12" s="3">
-        <v>6700</v>
+        <v>7000</v>
       </c>
       <c r="I12" s="3">
+        <v>6100</v>
+      </c>
+      <c r="J12" s="3">
+        <v>6400</v>
+      </c>
+      <c r="K12" s="3">
         <v>5500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>5400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>4500</v>
-      </c>
-      <c r="L12" s="3">
-        <v>3900</v>
-      </c>
-      <c r="M12" s="3">
-        <v>4400</v>
       </c>
       <c r="N12" s="3">
         <v>3900</v>
       </c>
       <c r="O12" s="3">
+        <v>4400</v>
+      </c>
+      <c r="P12" s="3">
+        <v>3900</v>
+      </c>
+      <c r="Q12" s="3">
         <v>4600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>4600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>2400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>2700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>2500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>2600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>2200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>2700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>1800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>2300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>1000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>2000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>1700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>2100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>3100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>2300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>2200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>1900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>1400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,83 +1355,89 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3">
         <v>-200</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>4</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA14" s="3">
         <v>1700</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1413,28 +1453,34 @@
       <c r="AF14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
@@ -1517,8 +1563,14 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1602,218 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>13700</v>
+      </c>
+      <c r="F17" s="3">
         <v>12000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>12500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>9400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>8300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>8700</v>
-      </c>
-      <c r="I17" s="3">
-        <v>7400</v>
-      </c>
-      <c r="J17" s="3">
-        <v>7800</v>
       </c>
       <c r="K17" s="3">
         <v>7400</v>
       </c>
       <c r="L17" s="3">
+        <v>7800</v>
+      </c>
+      <c r="M17" s="3">
+        <v>7400</v>
+      </c>
+      <c r="N17" s="3">
         <v>6100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>5900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>5800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>6000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>6400</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>3600</v>
-      </c>
-      <c r="R17" s="3">
-        <v>3900</v>
       </c>
       <c r="S17" s="3">
         <v>3600</v>
       </c>
       <c r="T17" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="U17" s="3">
-        <v>3400</v>
+        <v>3600</v>
       </c>
       <c r="V17" s="3">
         <v>4000</v>
       </c>
       <c r="W17" s="3">
+        <v>3400</v>
+      </c>
+      <c r="X17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Y17" s="3">
         <v>3200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>3600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>3900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>3100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2900</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>3500</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>4100</v>
       </c>
       <c r="AD17" s="3">
         <v>3500</v>
       </c>
       <c r="AE17" s="3">
+        <v>4100</v>
+      </c>
+      <c r="AF17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AG17" s="3">
         <v>3200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>2800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>2600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-13300</v>
       </c>
       <c r="E18" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="G18" s="3">
         <v>-12500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-9400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-8300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-8700</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-7800</v>
       </c>
       <c r="K18" s="3">
         <v>-7400</v>
       </c>
       <c r="L18" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="N18" s="3">
         <v>-6100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-5900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-5800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-6000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-6400</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-3900</v>
       </c>
       <c r="S18" s="3">
         <v>-3600</v>
       </c>
       <c r="T18" s="3">
-        <v>-4000</v>
+        <v>-3900</v>
       </c>
       <c r="U18" s="3">
-        <v>-3400</v>
+        <v>-3600</v>
       </c>
       <c r="V18" s="3">
         <v>-4000</v>
       </c>
       <c r="W18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="X18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-3200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-2900</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>-4100</v>
       </c>
       <c r="AD18" s="3">
         <v>-3500</v>
       </c>
       <c r="AE18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,86 +1848,88 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>1700</v>
       </c>
       <c r="E20" s="3">
-        <v>5000</v>
+        <v>-12500</v>
       </c>
       <c r="F20" s="3">
-        <v>-4300</v>
+        <v>15000</v>
       </c>
       <c r="G20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H20" s="3">
+        <v>8200</v>
+      </c>
+      <c r="I20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
@@ -1869,66 +1937,72 @@
         <v>0</v>
       </c>
       <c r="AE20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG20" s="3">
         <v>100</v>
       </c>
       <c r="AH20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-14900</v>
       </c>
       <c r="E21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="M21" s="3">
         <v>-7400</v>
       </c>
-      <c r="F21" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-8500</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-6100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-5900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-5800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-6000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-6300</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-3900</v>
       </c>
       <c r="S21" s="3">
         <v>-3600</v>
@@ -1937,72 +2011,78 @@
         <v>-3900</v>
       </c>
       <c r="U21" s="3">
-        <v>-3300</v>
+        <v>-3600</v>
       </c>
       <c r="V21" s="3">
         <v>-3900</v>
       </c>
       <c r="W21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="X21" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-3200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2076,133 +2156,145 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-21600</v>
+        <v>-14700</v>
       </c>
       <c r="E23" s="3">
-        <v>-7500</v>
+        <v>-900</v>
       </c>
       <c r="F23" s="3">
-        <v>-13700</v>
+        <v>-26600</v>
       </c>
       <c r="G23" s="3">
-        <v>-8200</v>
+        <v>-12300</v>
       </c>
       <c r="H23" s="3">
-        <v>-8600</v>
+        <v>-17500</v>
       </c>
       <c r="I23" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="K23" s="3">
         <v>-7300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-7800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-7400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-6100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-5900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-5800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-6000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-6400</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-3900</v>
       </c>
       <c r="S23" s="3">
         <v>-3600</v>
       </c>
       <c r="T23" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="U23" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="V23" s="3">
         <v>-4000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-3400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-3900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-3200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-2900</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>-4100</v>
       </c>
       <c r="AD23" s="3">
         <v>-3500</v>
       </c>
       <c r="AE23" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="AF23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="AG23" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2215,11 +2307,11 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -2272,8 +2364,14 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2468,222 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-21600</v>
+        <v>-14700</v>
       </c>
       <c r="E26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="M26" s="3">
         <v>-7400</v>
       </c>
-      <c r="F26" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-6100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-5900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-5800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-6000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-6400</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-3900</v>
       </c>
       <c r="S26" s="3">
         <v>-3600</v>
       </c>
       <c r="T26" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="U26" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="V26" s="3">
         <v>-4000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-3400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-3900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-3200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-2900</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>-4100</v>
       </c>
       <c r="AD26" s="3">
         <v>-3500</v>
       </c>
       <c r="AE26" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="AF26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="AG26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-21600</v>
+        <v>-14700</v>
       </c>
       <c r="E27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="M27" s="3">
         <v>-7400</v>
       </c>
-      <c r="F27" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-6100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-5900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-5800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-6000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-6400</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-3900</v>
       </c>
       <c r="S27" s="3">
         <v>-3600</v>
       </c>
       <c r="T27" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="U27" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="V27" s="3">
         <v>-4000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-3400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-3900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-3200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-2900</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>-5500</v>
       </c>
       <c r="AD27" s="3">
         <v>-3500</v>
       </c>
       <c r="AE27" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="AF27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2780,14 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2884,14 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2988,14 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,86 +3092,92 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>-1700</v>
       </c>
       <c r="E32" s="3">
-        <v>-5000</v>
+        <v>12500</v>
       </c>
       <c r="F32" s="3">
-        <v>4300</v>
+        <v>-15000</v>
       </c>
       <c r="G32" s="3">
+        <v>100</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
@@ -3045,117 +3185,129 @@
         <v>0</v>
       </c>
       <c r="AE32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG32" s="3">
         <v>-100</v>
       </c>
       <c r="AH32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-21600</v>
+        <v>-14700</v>
       </c>
       <c r="E33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="K33" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="M33" s="3">
         <v>-7400</v>
       </c>
-      <c r="F33" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-6100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-5900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-5800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-6000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-6400</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-3900</v>
       </c>
       <c r="S33" s="3">
         <v>-3600</v>
       </c>
       <c r="T33" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="U33" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="V33" s="3">
         <v>-4000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-3400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-3900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-3200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-2900</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>-5500</v>
       </c>
       <c r="AD33" s="3">
         <v>-3500</v>
       </c>
       <c r="AE33" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="AF33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="AG33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3404,227 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-21600</v>
+        <v>-14700</v>
       </c>
       <c r="E35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="K35" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="M35" s="3">
         <v>-7400</v>
       </c>
-      <c r="F35" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-6100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-5900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-5800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-6000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-6400</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-3900</v>
       </c>
       <c r="S35" s="3">
         <v>-3600</v>
       </c>
       <c r="T35" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="U35" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="V35" s="3">
         <v>-4000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-3400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-3900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-3200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-2900</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>-5500</v>
       </c>
       <c r="AD35" s="3">
         <v>-3500</v>
       </c>
       <c r="AE35" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="AF35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="AG35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3659,10 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3697,114 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>25900</v>
+      </c>
+      <c r="F41" s="3">
         <v>40000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>9600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>19000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>5200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>12700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>19900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>17800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>24800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>30600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>35700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>40300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>46800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>53600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>57200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>18800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>22500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>7100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>10600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>13300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>16800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>10500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>13300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>16400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>4200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>6800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>10000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>5700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>8300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>11200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>11400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,31 +3901,37 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3819,31 +4005,37 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3917,227 +4109,245 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
+        <v>700</v>
+      </c>
+      <c r="L45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M45" s="3">
+        <v>500</v>
+      </c>
+      <c r="N45" s="3">
+        <v>800</v>
+      </c>
+      <c r="O45" s="3">
+        <v>900</v>
+      </c>
+      <c r="P45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>300</v>
+      </c>
+      <c r="R45" s="3">
+        <v>800</v>
+      </c>
+      <c r="S45" s="3">
+        <v>800</v>
+      </c>
+      <c r="T45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U45" s="3">
+        <v>600</v>
+      </c>
+      <c r="V45" s="3">
+        <v>800</v>
+      </c>
+      <c r="W45" s="3">
+        <v>800</v>
+      </c>
+      <c r="X45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y45" s="3">
         <v>1300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="Z45" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>700</v>
+      </c>
+      <c r="AC45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AD45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AE45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AH45" s="3">
         <v>900</v>
       </c>
-      <c r="F45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="AI45" s="3">
+        <v>700</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>500</v>
       </c>
-      <c r="H45" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>700</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>500</v>
-      </c>
-      <c r="L45" s="3">
-        <v>800</v>
-      </c>
-      <c r="M45" s="3">
-        <v>900</v>
-      </c>
-      <c r="N45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="O45" s="3">
-        <v>300</v>
-      </c>
-      <c r="P45" s="3">
-        <v>800</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>800</v>
-      </c>
-      <c r="R45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="S45" s="3">
-        <v>600</v>
-      </c>
-      <c r="T45" s="3">
-        <v>800</v>
-      </c>
-      <c r="U45" s="3">
-        <v>800</v>
-      </c>
-      <c r="V45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="W45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="X45" s="3">
-        <v>600</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>700</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>700</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>800</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>800</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>500</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AE45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AF45" s="3">
-        <v>900</v>
-      </c>
-      <c r="AG45" s="3">
-        <v>700</v>
-      </c>
-      <c r="AH45" s="3">
-        <v>500</v>
-      </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>27900</v>
+      </c>
+      <c r="F46" s="3">
         <v>41400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>10500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>20100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>5600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>13800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>20500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>18800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>25300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>31400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>36600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>41400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>47100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>54400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>57900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>19800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>23000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>7900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>11400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>14800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>18200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>11100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>14000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>17100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>5000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>7600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>10500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>6700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>9300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>12200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>12200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4211,34 +4421,40 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F48" s="3">
         <v>1500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1000</v>
-      </c>
-      <c r="J48" s="3">
-        <v>500</v>
-      </c>
-      <c r="K48" s="3">
-        <v>500</v>
       </c>
       <c r="L48" s="3">
         <v>500</v>
@@ -4253,40 +4469,40 @@
         <v>500</v>
       </c>
       <c r="P48" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>500</v>
+      </c>
+      <c r="R48" s="3">
         <v>600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>600</v>
-      </c>
-      <c r="R48" s="3">
-        <v>700</v>
-      </c>
-      <c r="S48" s="3">
-        <v>700</v>
       </c>
       <c r="T48" s="3">
         <v>700</v>
       </c>
       <c r="U48" s="3">
+        <v>700</v>
+      </c>
+      <c r="V48" s="3">
+        <v>700</v>
+      </c>
+      <c r="W48" s="3">
         <v>800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>500</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>200</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>200</v>
       </c>
       <c r="AB48" s="3">
         <v>200</v>
@@ -4295,22 +4511,28 @@
         <v>200</v>
       </c>
       <c r="AD48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF48" s="3">
         <v>1500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>1600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>1400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>1400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4381,10 +4603,10 @@
         <v>0</v>
       </c>
       <c r="Z49" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="AA49" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="AB49" s="3">
         <v>1700</v>
@@ -4407,8 +4629,14 @@
       <c r="AH49" s="3">
         <v>1700</v>
       </c>
+      <c r="AI49" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AJ49" s="3">
+        <v>1700</v>
+      </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4733,14 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,8 +4837,14 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4621,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
@@ -4651,13 +4891,13 @@
         <v>100</v>
       </c>
       <c r="R52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S52" s="3">
         <v>100</v>
       </c>
       <c r="T52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U52" s="3">
         <v>100</v>
@@ -4669,29 +4909,29 @@
         <v>100</v>
       </c>
       <c r="X52" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z52" s="3">
         <v>500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>100</v>
       </c>
-      <c r="AB52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="3">
         <v>500</v>
       </c>
-      <c r="AD52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>0</v>
-      </c>
       <c r="AF52" s="3">
         <v>0</v>
       </c>
@@ -4701,8 +4941,14 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +5045,118 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>37300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>29400</v>
+      </c>
+      <c r="F54" s="3">
         <v>42900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>12100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>21600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>6500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>14800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>21600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>19300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>25900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>32000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>37200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>42000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>47700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>55100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>58700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>20700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>23900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>8700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>12300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>15700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>19100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>12500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>15100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>19500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>7000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>9600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>12900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>9900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>12600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>15300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>15300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>9300</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5191,10 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,129 +5229,137 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F57" s="3">
         <v>7400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>9200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>7800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>6400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>6900</v>
-      </c>
-      <c r="I57" s="3">
-        <v>5500</v>
-      </c>
-      <c r="J57" s="3">
-        <v>6400</v>
       </c>
       <c r="K57" s="3">
         <v>5500</v>
       </c>
       <c r="L57" s="3">
+        <v>6400</v>
+      </c>
+      <c r="M57" s="3">
+        <v>5500</v>
+      </c>
+      <c r="N57" s="3">
         <v>4500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>3900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>3000</v>
-      </c>
-      <c r="O57" s="3">
-        <v>3400</v>
-      </c>
-      <c r="P57" s="3">
-        <v>4900</v>
       </c>
       <c r="Q57" s="3">
         <v>3400</v>
       </c>
       <c r="R57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="S57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="T57" s="3">
         <v>3800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>3200</v>
-      </c>
-      <c r="T57" s="3">
-        <v>2900</v>
-      </c>
-      <c r="U57" s="3">
-        <v>2700</v>
       </c>
       <c r="V57" s="3">
         <v>2900</v>
       </c>
       <c r="W57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="X57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="Y57" s="3">
         <v>2500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>2100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>2600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>2100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>1900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>1900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>2000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>1500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>1200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>1400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5160,36 +5428,42 @@
         <v>0</v>
       </c>
       <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3">
         <v>100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>8900</v>
+        <v>11900</v>
       </c>
       <c r="E59" s="3">
-        <v>3800</v>
+        <v>8600</v>
       </c>
       <c r="F59" s="3">
-        <v>8700</v>
+        <v>21100</v>
       </c>
       <c r="G59" s="3">
-        <v>100</v>
+        <v>16100</v>
       </c>
       <c r="H59" s="3">
-        <v>100</v>
-      </c>
-      <c r="I59" s="3">
-        <v>100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>100</v>
+        <v>8600</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K59" s="3">
         <v>100</v>
@@ -5240,22 +5514,22 @@
         <v>100</v>
       </c>
       <c r="AA59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC59" s="3">
         <v>200</v>
       </c>
       <c r="AD59" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE59" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF59" s="3">
         <v>100</v>
-      </c>
-      <c r="AE59" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF59" s="3">
-        <v>200</v>
       </c>
       <c r="AG59" s="3">
         <v>100</v>
@@ -5263,97 +5537,103 @@
       <c r="AH59" s="3">
         <v>200</v>
       </c>
+      <c r="AI59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ59" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>16300</v>
+        <v>20300</v>
       </c>
       <c r="E60" s="3">
-        <v>12900</v>
+        <v>15200</v>
       </c>
       <c r="F60" s="3">
+        <v>28600</v>
+      </c>
+      <c r="G60" s="3">
+        <v>25400</v>
+      </c>
+      <c r="H60" s="3">
         <v>16500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>7000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>5500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>6500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>5600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>4700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>4000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>3500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>5000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>3600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>4000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>3300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>3100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>2800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>3000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>2700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>2200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>2700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>2300</v>
-      </c>
-      <c r="AB60" s="3">
-        <v>2100</v>
-      </c>
-      <c r="AC60" s="3">
-        <v>2100</v>
       </c>
       <c r="AD60" s="3">
         <v>2100</v>
       </c>
       <c r="AE60" s="3">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="AF60" s="3">
-        <v>1400</v>
+        <v>2100</v>
       </c>
       <c r="AG60" s="3">
         <v>1600</v>
@@ -5361,31 +5641,37 @@
       <c r="AH60" s="3">
         <v>1400</v>
       </c>
+      <c r="AI60" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AJ60" s="3">
+        <v>1400</v>
+      </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5409,17 +5695,17 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>200</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -5459,61 +5745,67 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>500</v>
-      </c>
-      <c r="E62" s="3">
-        <v>500</v>
-      </c>
-      <c r="F62" s="3">
-        <v>500</v>
-      </c>
-      <c r="G62" s="3">
-        <v>500</v>
-      </c>
-      <c r="H62" s="3">
-        <v>500</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>600</v>
-      </c>
-      <c r="J62" s="3">
-        <v>100</v>
-      </c>
-      <c r="K62" s="3">
-        <v>100</v>
       </c>
       <c r="L62" s="3">
         <v>100</v>
       </c>
       <c r="M62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O62" s="3">
         <v>200</v>
       </c>
       <c r="P62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="R62" s="3">
         <v>300</v>
       </c>
       <c r="S62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="T62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="U62" s="3">
         <v>400</v>
@@ -5522,31 +5814,31 @@
         <v>400</v>
       </c>
       <c r="W62" s="3">
+        <v>400</v>
+      </c>
+      <c r="X62" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y62" s="3">
         <v>500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>200</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>100</v>
+      <c r="AC62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF62" s="3">
         <v>100</v>
@@ -5557,8 +5849,14 @@
       <c r="AH62" s="3">
         <v>100</v>
       </c>
+      <c r="AI62" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ62" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5953,14 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +6057,14 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,64 +6161,70 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>16700</v>
+        <v>20700</v>
       </c>
       <c r="E66" s="3">
-        <v>13400</v>
+        <v>15600</v>
       </c>
       <c r="F66" s="3">
+        <v>29000</v>
+      </c>
+      <c r="G66" s="3">
+        <v>25900</v>
+      </c>
+      <c r="H66" s="3">
         <v>17000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>7000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>7500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>6100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>6600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>5700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>4800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>4200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>3800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>5300</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>3900</v>
-      </c>
-      <c r="R66" s="3">
-        <v>4500</v>
       </c>
       <c r="S66" s="3">
         <v>3900</v>
       </c>
       <c r="T66" s="3">
-        <v>3400</v>
+        <v>4500</v>
       </c>
       <c r="U66" s="3">
-        <v>3200</v>
+        <v>3900</v>
       </c>
       <c r="V66" s="3">
         <v>3400</v>
@@ -5917,40 +6233,46 @@
         <v>3200</v>
       </c>
       <c r="X66" s="3">
-        <v>2700</v>
+        <v>3400</v>
       </c>
       <c r="Y66" s="3">
-        <v>1800</v>
+        <v>3200</v>
       </c>
       <c r="Z66" s="3">
         <v>2700</v>
       </c>
       <c r="AA66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AB66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AC66" s="3">
         <v>2300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>2100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>2100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>2300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>1700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>1500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>1800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6307,10 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6407,14 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,25 +6511,31 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>17100</v>
+        <v>15000</v>
       </c>
       <c r="E70" s="3">
+        <v>9200</v>
+      </c>
+      <c r="F70" s="3">
+        <v>18400</v>
+      </c>
+      <c r="G70" s="3">
         <v>6100</v>
       </c>
-      <c r="F70" s="3">
+      <c r="H70" s="3">
         <v>19300</v>
-      </c>
-      <c r="G70" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H70" s="3">
-        <v>1400</v>
       </c>
       <c r="I70" s="3">
         <v>1400</v>
@@ -6220,19 +6556,19 @@
         <v>1400</v>
       </c>
       <c r="O70" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P70" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q70" s="3">
         <v>8600</v>
       </c>
-      <c r="P70" s="3">
+      <c r="R70" s="3">
         <v>11700</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="S70" s="3">
         <v>20000</v>
-      </c>
-      <c r="R70" s="3">
-        <v>1100</v>
-      </c>
-      <c r="S70" s="3">
-        <v>1100</v>
       </c>
       <c r="T70" s="3">
         <v>1100</v>
@@ -6247,40 +6583,46 @@
         <v>1100</v>
       </c>
       <c r="X70" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Z70" s="3">
         <v>1800</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="AA70" s="3">
         <v>2500</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AB70" s="3">
         <v>3500</v>
       </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="3">
         <v>600</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AE70" s="3">
         <v>1000</v>
       </c>
-      <c r="AD70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE70" s="3">
-        <v>0</v>
-      </c>
       <c r="AF70" s="3">
         <v>0</v>
       </c>
       <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
         <v>900</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AJ70" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6719,118 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-239100</v>
+        <v>-245000</v>
       </c>
       <c r="E72" s="3">
-        <v>-217500</v>
+        <v>-230300</v>
       </c>
       <c r="F72" s="3">
+        <v>-229400</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-202800</v>
+      </c>
+      <c r="H72" s="3">
         <v>-210000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-196300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-188100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-179500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-172300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-164500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-157000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-150900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-145000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-139200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-133100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-126800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-123200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-119300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-115600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-111700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-108300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-104400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-101200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-97600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-93800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-90700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-87800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-84300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-80300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-76800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-73700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-70800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>-68200</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6927,14 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +7031,14 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +7135,118 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>9100</v>
+        <v>1500</v>
       </c>
       <c r="E76" s="3">
-        <v>-7400</v>
+        <v>4500</v>
       </c>
       <c r="F76" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="G76" s="3">
+        <v>-19800</v>
+      </c>
+      <c r="H76" s="3">
         <v>-14700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-1800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>6000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>14100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>11400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>18800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>25800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>31700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>37200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>35300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>38000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>34800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>15100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>18800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>4100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>7900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>11100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>14800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>8100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>10700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>13400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>4700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>6800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>9800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>7600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>10900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>13700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>12700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7343,227 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-21600</v>
+        <v>-14700</v>
       </c>
       <c r="E81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="K81" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="M81" s="3">
         <v>-7400</v>
       </c>
-      <c r="F81" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-6100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-5900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-5800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-6000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-6400</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-3900</v>
       </c>
       <c r="S81" s="3">
         <v>-3600</v>
       </c>
       <c r="T81" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="U81" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="V81" s="3">
         <v>-4000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-3400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-3900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-3200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-2900</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>-5500</v>
       </c>
       <c r="AD81" s="3">
         <v>-3500</v>
       </c>
       <c r="AE81" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="AF81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="AG81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,16 +7598,18 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -7283,13 +7681,13 @@
         <v>0</v>
       </c>
       <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3">
         <v>1300</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>100</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>100</v>
       </c>
       <c r="AF83" s="3">
         <v>100</v>
@@ -7300,8 +7698,14 @@
       <c r="AH83" s="3">
         <v>100</v>
       </c>
+      <c r="AI83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7802,14 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7906,14 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +8010,14 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +8114,14 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,64 +8218,70 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-13400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-9600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-8100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-7500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-7200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-7400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-7000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-5800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-5000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-4500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-6400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-6900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-3900</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-3000</v>
       </c>
       <c r="T89" s="3">
         <v>-3500</v>
       </c>
       <c r="U89" s="3">
-        <v>-2700</v>
+        <v>-3000</v>
       </c>
       <c r="V89" s="3">
         <v>-3500</v>
@@ -7856,40 +8290,46 @@
         <v>-2700</v>
       </c>
       <c r="X89" s="3">
-        <v>-2800</v>
+        <v>-3500</v>
       </c>
       <c r="Y89" s="3">
         <v>-2700</v>
       </c>
       <c r="Z89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="AA89" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8364,10 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7933,22 +8375,22 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-600</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
@@ -7962,17 +8404,17 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="O91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -7993,14 +8435,14 @@
         <v>0</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-400</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
       <c r="AB91" s="3">
         <v>0</v>
       </c>
@@ -8011,19 +8453,25 @@
         <v>0</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8568,14 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,8 +8672,14 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8227,22 +8687,22 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-600</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K94" s="3">
         <v>-100</v>
@@ -8256,17 +8716,17 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="O94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
@@ -8287,14 +8747,14 @@
         <v>0</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-400</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
       <c r="AB94" s="3">
         <v>0</v>
       </c>
@@ -8305,19 +8765,25 @@
         <v>0</v>
       </c>
       <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,31 +8818,33 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8450,8 +8918,14 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +9022,14 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +9126,14 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,35 +9230,41 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>43800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>22500</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>9600</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
@@ -8786,87 +9278,93 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>1200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>42200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>18400</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>9000</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>15100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-100</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>7200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-100</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>2800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>8200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -8940,102 +9438,114 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="F102" s="3">
         <v>30500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-9400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>13800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-7500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-7200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>2100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-7000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-5800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-5100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-4600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-6400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-6800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>38300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-3600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>15400</v>
-      </c>
-      <c r="T102" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="U102" s="3">
-        <v>-2700</v>
       </c>
       <c r="V102" s="3">
         <v>-3500</v>
       </c>
       <c r="W102" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="X102" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="Y102" s="3">
         <v>6400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>12200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>4300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>5800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-2300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CLRB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CLRB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
   <si>
     <t>CLRB</t>
   </si>
@@ -656,155 +656,158 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -829,8 +832,8 @@
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -907,8 +910,11 @@
       <c r="AJ8" s="3">
         <v>0</v>
       </c>
+      <c r="AK8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1011,8 +1017,11 @@
       <c r="AJ9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1115,8 +1124,11 @@
       <c r="AJ10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,112 +1165,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E12" s="3">
         <v>5500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
+        <v>7700</v>
+      </c>
+      <c r="I12" s="3">
         <v>7000</v>
       </c>
-      <c r="H12" s="3">
-        <v>7000</v>
-      </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3900</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>4600</v>
       </c>
       <c r="R12" s="3">
         <v>4600</v>
       </c>
       <c r="S12" s="3">
+        <v>4600</v>
+      </c>
+      <c r="T12" s="3">
         <v>2400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>2300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>2000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>2100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>3100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>2300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>2200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,8 +1377,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1387,23 +1406,23 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>4</v>
@@ -1411,23 +1430,23 @@
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T14" s="3">
         <v>-200</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>4</v>
+      <c r="W14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>4</v>
@@ -1435,12 +1454,12 @@
       <c r="Z14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB14" s="3">
         <v>1700</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1459,14 +1478,17 @@
       <c r="AH14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
+      <c r="AI14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1483,7 +1505,7 @@
         <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
@@ -1569,8 +1591,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E17" s="3">
         <v>13300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-13300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-12000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-12500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-9400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-6000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-4000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,38 +1882,39 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E20" s="3">
         <v>1700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-12500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>15000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-100</v>
-      </c>
       <c r="H20" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="I20" s="3">
         <v>8200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1916,22 +1949,22 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
       <c r="AA20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="3">
         <v>100</v>
       </c>
       <c r="AC20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD20" s="3">
         <v>0</v>
@@ -1943,123 +1976,129 @@
         <v>0</v>
       </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-14900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-26900</v>
       </c>
-      <c r="G21" s="3">
-        <v>-12400</v>
-      </c>
       <c r="H21" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="I21" s="3">
         <v>-17500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-10200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-7300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-7200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-7800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-6000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-6300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-3600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-3900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-3400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2084,8 +2123,8 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2162,117 +2201,123 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-14700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-26600</v>
       </c>
-      <c r="G23" s="3">
-        <v>-12300</v>
-      </c>
       <c r="H23" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="I23" s="3">
         <v>-17500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-10200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>4</v>
+      <c r="D24" s="3">
+        <v>100</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>4</v>
@@ -2280,24 +2325,24 @@
       <c r="F24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2313,8 +2358,8 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="R24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
@@ -2370,8 +2415,11 @@
       <c r="AJ24" s="3">
         <v>0</v>
       </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-14700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-26600</v>
       </c>
-      <c r="G26" s="3">
-        <v>-12200</v>
-      </c>
       <c r="H26" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="I26" s="3">
         <v>-17500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10200</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-7200</v>
       </c>
       <c r="K26" s="3">
         <v>-7200</v>
       </c>
       <c r="L26" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="M26" s="3">
         <v>-7800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-6100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-14700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-26600</v>
       </c>
-      <c r="G27" s="3">
-        <v>-12200</v>
-      </c>
       <c r="H27" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="I27" s="3">
         <v>-17500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-10200</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-7200</v>
       </c>
       <c r="K27" s="3">
         <v>-7200</v>
       </c>
       <c r="L27" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="M27" s="3">
         <v>-7800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-5500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,38 +3164,41 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>12500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-15000</v>
       </c>
-      <c r="G32" s="3">
-        <v>100</v>
-      </c>
       <c r="H32" s="3">
+        <v>4500</v>
+      </c>
+      <c r="I32" s="3">
         <v>-8200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -3164,22 +3233,22 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
       <c r="AA32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB32" s="3">
         <v>-100</v>
       </c>
       <c r="AC32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD32" s="3">
         <v>0</v>
@@ -3191,123 +3260,129 @@
         <v>0</v>
       </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-14700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-26600</v>
       </c>
-      <c r="G33" s="3">
-        <v>-12200</v>
-      </c>
       <c r="H33" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="I33" s="3">
         <v>-17500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-10200</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-7200</v>
       </c>
       <c r="K33" s="3">
         <v>-7200</v>
       </c>
       <c r="L33" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="M33" s="3">
         <v>-7800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-6400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-5500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-14700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-26600</v>
       </c>
-      <c r="G35" s="3">
-        <v>-12200</v>
-      </c>
       <c r="H35" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="I35" s="3">
         <v>-17500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-10200</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-7200</v>
       </c>
       <c r="K35" s="3">
         <v>-7200</v>
       </c>
       <c r="L35" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="M35" s="3">
         <v>-7800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-6400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-5500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3784,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E41" s="3">
         <v>34300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>25900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>40000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>19000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>12700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>19900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>17800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>24800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>30600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>35700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>40300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>46800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>53600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>57200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>18800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>22500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>13300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>16800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>10500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>13300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>16400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>10000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>8300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>11200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>11400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3907,8 +3996,11 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3933,8 +4025,8 @@
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -4011,8 +4103,11 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4037,8 +4132,8 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4115,8 +4210,11 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4141,190 +4239,196 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>300</v>
-      </c>
-      <c r="R45" s="3">
-        <v>800</v>
       </c>
       <c r="S45" s="3">
         <v>800</v>
       </c>
       <c r="T45" s="3">
+        <v>800</v>
+      </c>
+      <c r="U45" s="3">
         <v>1000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>600</v>
-      </c>
-      <c r="V45" s="3">
-        <v>800</v>
       </c>
       <c r="W45" s="3">
         <v>800</v>
       </c>
       <c r="X45" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y45" s="3">
         <v>1500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>600</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>700</v>
       </c>
       <c r="AB45" s="3">
         <v>700</v>
       </c>
       <c r="AC45" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="AD45" s="3">
         <v>800</v>
       </c>
       <c r="AE45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AF45" s="3">
         <v>500</v>
-      </c>
-      <c r="AF45" s="3">
-        <v>1000</v>
       </c>
       <c r="AG45" s="3">
         <v>1000</v>
       </c>
       <c r="AH45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AI45" s="3">
         <v>900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E46" s="3">
         <v>35900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>27900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>41400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>20100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>20500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>18800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>25300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>31400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>36600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>41400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>47100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>54400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>57900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>19800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>23000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>11400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>14800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>18200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>11100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>14000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>17100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>10500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>9300</v>
-      </c>
-      <c r="AH46" s="3">
-        <v>12200</v>
       </c>
       <c r="AI46" s="3">
         <v>12200</v>
       </c>
       <c r="AJ46" s="3">
+        <v>12200</v>
+      </c>
+      <c r="AK46" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4349,8 +4453,8 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4427,37 +4531,40 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="E48" s="3">
         <v>1400</v>
       </c>
       <c r="F48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G48" s="3">
         <v>1500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1400</v>
-      </c>
-      <c r="I48" s="3">
-        <v>900</v>
       </c>
       <c r="J48" s="3">
         <v>900</v>
       </c>
       <c r="K48" s="3">
+        <v>900</v>
+      </c>
+      <c r="L48" s="3">
         <v>1000</v>
-      </c>
-      <c r="L48" s="3">
-        <v>500</v>
       </c>
       <c r="M48" s="3">
         <v>500</v>
@@ -4475,13 +4582,13 @@
         <v>500</v>
       </c>
       <c r="R48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="S48" s="3">
         <v>600</v>
       </c>
       <c r="T48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="U48" s="3">
         <v>700</v>
@@ -4490,22 +4597,22 @@
         <v>700</v>
       </c>
       <c r="W48" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="X48" s="3">
         <v>800</v>
       </c>
       <c r="Y48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="Z48" s="3">
         <v>900</v>
       </c>
       <c r="AA48" s="3">
+        <v>900</v>
+      </c>
+      <c r="AB48" s="3">
         <v>500</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>200</v>
       </c>
       <c r="AC48" s="3">
         <v>200</v>
@@ -4517,22 +4624,25 @@
         <v>200</v>
       </c>
       <c r="AF48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG48" s="3">
         <v>1500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1600</v>
-      </c>
-      <c r="AH48" s="3">
-        <v>1400</v>
       </c>
       <c r="AI48" s="3">
         <v>1400</v>
       </c>
       <c r="AJ48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AK48" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4609,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="AB49" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="AC49" s="3">
         <v>1700</v>
@@ -4635,8 +4745,11 @@
       <c r="AJ49" s="3">
         <v>1700</v>
       </c>
+      <c r="AK49" s="3">
+        <v>1700</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,8 +4959,11 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4867,7 +4986,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K52" s="3">
         <v>100</v>
@@ -4897,10 +5016,10 @@
         <v>100</v>
       </c>
       <c r="T52" s="3">
+        <v>100</v>
+      </c>
+      <c r="U52" s="3">
         <v>200</v>
-      </c>
-      <c r="U52" s="3">
-        <v>100</v>
       </c>
       <c r="V52" s="3">
         <v>100</v>
@@ -4915,26 +5034,26 @@
         <v>100</v>
       </c>
       <c r="Z52" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA52" s="3">
         <v>500</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>600</v>
       </c>
       <c r="AB52" s="3">
         <v>600</v>
       </c>
       <c r="AC52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD52" s="3">
         <v>100</v>
       </c>
-      <c r="AD52" s="3">
-        <v>0</v>
-      </c>
       <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3">
         <v>500</v>
       </c>
-      <c r="AF52" s="3">
-        <v>0</v>
-      </c>
       <c r="AG52" s="3">
         <v>0</v>
       </c>
@@ -4947,8 +5066,11 @@
       <c r="AJ52" s="3">
         <v>0</v>
       </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E54" s="3">
         <v>37300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>29400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>42900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>25900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>37200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>42000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>47700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>55100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>58700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>20700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>23900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>8700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>12300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>15700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>19100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>12500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>15100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>19500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>9600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>12900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>9900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12600</v>
-      </c>
-      <c r="AH54" s="3">
-        <v>15300</v>
       </c>
       <c r="AI54" s="3">
         <v>15300</v>
       </c>
       <c r="AJ54" s="3">
+        <v>15300</v>
+      </c>
+      <c r="AK54" s="3">
         <v>9300</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,112 +5360,116 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E57" s="3">
         <v>8300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2100</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>1900</v>
       </c>
       <c r="AE57" s="3">
         <v>1900</v>
       </c>
       <c r="AF57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AG57" s="3">
         <v>2000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5362,7 +5495,7 @@
         <v>100</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -5434,39 +5567,42 @@
         <v>0</v>
       </c>
       <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E59" s="3">
         <v>11900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>21100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8600</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
-        <v>100</v>
+      <c r="K59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L59" s="3">
         <v>100</v>
@@ -5520,7 +5656,7 @@
         <v>100</v>
       </c>
       <c r="AC59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD59" s="3">
         <v>200</v>
@@ -5529,105 +5665,108 @@
         <v>200</v>
       </c>
       <c r="AF59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AG59" s="3">
         <v>100</v>
       </c>
       <c r="AH59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI59" s="3">
         <v>200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E60" s="3">
         <v>20300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>28600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>25400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2300</v>
-      </c>
-      <c r="AD60" s="3">
-        <v>2100</v>
       </c>
       <c r="AE60" s="3">
         <v>2100</v>
@@ -5636,19 +5775,22 @@
         <v>2100</v>
       </c>
       <c r="AG60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AH60" s="3">
         <v>1600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5656,7 +5798,7 @@
         <v>400</v>
       </c>
       <c r="E61" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F61" s="3">
         <v>500</v>
@@ -5674,7 +5816,7 @@
         <v>500</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -5701,13 +5843,13 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="U61" s="3">
         <v>200</v>
       </c>
       <c r="V61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="W61" s="3">
         <v>0</v>
@@ -5751,8 +5893,11 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5777,11 +5922,11 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3">
         <v>600</v>
-      </c>
-      <c r="L62" s="3">
-        <v>100</v>
       </c>
       <c r="M62" s="3">
         <v>100</v>
@@ -5790,7 +5935,7 @@
         <v>100</v>
       </c>
       <c r="O62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P62" s="3">
         <v>200</v>
@@ -5799,7 +5944,7 @@
         <v>200</v>
       </c>
       <c r="R62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="S62" s="3">
         <v>300</v>
@@ -5808,7 +5953,7 @@
         <v>300</v>
       </c>
       <c r="U62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="V62" s="3">
         <v>400</v>
@@ -5820,28 +5965,28 @@
         <v>400</v>
       </c>
       <c r="Y62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Z62" s="3">
         <v>500</v>
       </c>
       <c r="AA62" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB62" s="3">
         <v>200</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE62" s="3">
-        <v>0</v>
+      <c r="AE62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG62" s="3">
         <v>100</v>
@@ -5855,8 +6000,11 @@
       <c r="AJ62" s="3">
         <v>100</v>
       </c>
+      <c r="AK62" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E66" s="3">
         <v>20700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>15600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>29000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>17000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2300</v>
-      </c>
-      <c r="AD66" s="3">
-        <v>2100</v>
       </c>
       <c r="AE66" s="3">
         <v>2100</v>
       </c>
       <c r="AF66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AG66" s="3">
         <v>2300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,28 +6681,31 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E70" s="3">
         <v>15000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>9200</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>18400</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>6100</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>19300</v>
-      </c>
-      <c r="I70" s="3">
-        <v>1400</v>
       </c>
       <c r="J70" s="3">
         <v>1400</v>
@@ -6562,16 +6729,16 @@
         <v>1400</v>
       </c>
       <c r="Q70" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R70" s="3">
         <v>8600</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>11700</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>20000</v>
-      </c>
-      <c r="T70" s="3">
-        <v>1100</v>
       </c>
       <c r="U70" s="3">
         <v>1100</v>
@@ -6589,26 +6756,26 @@
         <v>1100</v>
       </c>
       <c r="Z70" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AA70" s="3">
         <v>1800</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>2500</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>3500</v>
       </c>
-      <c r="AC70" s="3">
-        <v>0</v>
-      </c>
       <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
         <v>600</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>1000</v>
       </c>
-      <c r="AF70" s="3">
-        <v>0</v>
-      </c>
       <c r="AG70" s="3">
         <v>0</v>
       </c>
@@ -6616,13 +6783,16 @@
         <v>0</v>
       </c>
       <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="3">
         <v>900</v>
       </c>
-      <c r="AJ70" s="3">
+      <c r="AK70" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-247300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-245000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-230300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-229400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-202800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-210000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-196300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-188100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-179500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-172300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-164500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-157000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-150900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-145000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-139200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-133100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-126800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-123200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-119300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-115600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-111700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-108300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-104400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-101200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-97600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-93800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-90700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-87800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-84300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-80300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-76800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-73700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-70800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-68200</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-4600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-19800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-14700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>25800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>31700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>37200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>35300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>38000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>34800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>18800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>11100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>10900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>13700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-14700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-26600</v>
       </c>
-      <c r="G81" s="3">
-        <v>-12200</v>
-      </c>
       <c r="H81" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="I81" s="3">
         <v>-17500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-10200</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-7200</v>
       </c>
       <c r="K81" s="3">
         <v>-7200</v>
       </c>
       <c r="L81" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="M81" s="3">
         <v>-7800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-6400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-5500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,13 +7797,14 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
@@ -7687,10 +7885,10 @@
         <v>0</v>
       </c>
       <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3">
         <v>1300</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>100</v>
       </c>
       <c r="AG83" s="3">
         <v>100</v>
@@ -7704,8 +7902,11 @@
       <c r="AJ83" s="3">
         <v>100</v>
       </c>
+      <c r="AK83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-9200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-14100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-8100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,13 +8585,14 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -8381,43 +8601,43 @@
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>4</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -8441,11 +8661,11 @@
         <v>0</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-400</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
       <c r="AC91" s="3">
         <v>0</v>
       </c>
@@ -8459,19 +8679,22 @@
         <v>0</v>
       </c>
       <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AH91" s="3">
-        <v>-100</v>
       </c>
       <c r="AI91" s="3">
         <v>-100</v>
       </c>
       <c r="AJ91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,13 +8904,16 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -8693,43 +8922,43 @@
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-600</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
@@ -8753,11 +8982,11 @@
         <v>0</v>
       </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-400</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
       <c r="AC94" s="3">
         <v>0</v>
       </c>
@@ -8771,19 +9000,22 @@
         <v>0</v>
       </c>
       <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-300</v>
-      </c>
-      <c r="AH94" s="3">
-        <v>-100</v>
       </c>
       <c r="AI94" s="3">
         <v>-100</v>
       </c>
       <c r="AJ94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,8 +9079,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8924,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,38 +9478,41 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>17600</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>43800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>22500</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>9600</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
@@ -9284,20 +9529,20 @@
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>1200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>42200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>18400</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
@@ -9305,43 +9550,46 @@
         <v>0</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>9000</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>15100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-100</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>7200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-100</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
       <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>2800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>8200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9366,8 +9614,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9444,108 +9692,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E102" s="3">
         <v>8400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-14200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>30500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>13800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>38300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>15400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>6400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>12200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>4300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-2300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CLRB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CLRB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
   <si>
     <t>CLRB</t>
   </si>
@@ -656,158 +656,162 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -835,8 +839,8 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -913,8 +917,11 @@
       <c r="AK8" s="3">
         <v>0</v>
       </c>
+      <c r="AL8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1020,8 +1027,11 @@
       <c r="AK9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1127,8 +1137,11 @@
       <c r="AK10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1166,115 +1179,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E12" s="3">
         <v>6200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>7700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3900</v>
-      </c>
-      <c r="R12" s="3">
-        <v>4600</v>
       </c>
       <c r="S12" s="3">
         <v>4600</v>
       </c>
       <c r="T12" s="3">
+        <v>4600</v>
+      </c>
+      <c r="U12" s="3">
         <v>2400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>2700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>2300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>2000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>2100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>3100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>2300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>2200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1400</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,8 +1397,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1409,23 +1429,23 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>4</v>
@@ -1433,23 +1453,23 @@
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U14" s="3">
         <v>-200</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>4</v>
+      <c r="X14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>4</v>
@@ -1457,12 +1477,12 @@
       <c r="AA14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC14" s="3">
         <v>1700</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1481,14 +1501,17 @@
       <c r="AI14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
+      <c r="AJ14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1508,7 +1531,7 @@
         <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -1594,8 +1617,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E17" s="3">
         <v>12700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-12700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-12000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-12500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-9400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-6400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-4000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-4100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,41 +1916,42 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-10200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-12500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>15000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>8200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1952,22 +1986,22 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
       <c r="AB20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC20" s="3">
         <v>100</v>
       </c>
       <c r="AD20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE20" s="3">
         <v>0</v>
@@ -1979,126 +2013,132 @@
         <v>0</v>
       </c>
       <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
         <v>100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-14900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-26900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-8000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-17500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-10200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-7300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-7200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-7400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-6100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-5800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-6000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-6300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-3600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-2800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2126,8 +2166,8 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2204,148 +2244,154 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-14700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-26600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-17500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-4000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F24" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2361,8 +2407,8 @@
       <c r="R24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -2418,8 +2464,11 @@
       <c r="AK24" s="3">
         <v>0</v>
       </c>
+      <c r="AL24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-14700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-26600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-17500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10200</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-7200</v>
       </c>
       <c r="L26" s="3">
         <v>-7200</v>
       </c>
       <c r="M26" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="N26" s="3">
         <v>-7800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-14700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-26600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-17500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10200</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-7200</v>
       </c>
       <c r="L27" s="3">
         <v>-7200</v>
       </c>
       <c r="M27" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="N27" s="3">
         <v>-7800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-5300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-5500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,41 +3234,44 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E32" s="3">
         <v>10200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>12500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-15000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-8200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -3236,22 +3306,22 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
       <c r="AB32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC32" s="3">
         <v>-100</v>
       </c>
       <c r="AD32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE32" s="3">
         <v>0</v>
@@ -3263,126 +3333,132 @@
         <v>0</v>
       </c>
       <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-14700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-26600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-17500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10200</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-7200</v>
       </c>
       <c r="L33" s="3">
         <v>-7200</v>
       </c>
       <c r="M33" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="N33" s="3">
         <v>-7800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-6000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-5300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-5500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-14700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-26600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-17500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10200</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-7200</v>
       </c>
       <c r="L35" s="3">
         <v>-7200</v>
       </c>
       <c r="M35" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="N35" s="3">
         <v>-7800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-6000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-5300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-5500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,115 +3871,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E41" s="3">
         <v>23300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>34300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>25900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>40000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>19000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>19900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>17800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>24800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>30600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>35700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>40300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>46800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>53600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>57200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>18800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>22500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>13300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>16800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>10500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>13300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>16400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>10000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>8300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>11200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>11400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3999,8 +4089,11 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4028,8 +4121,8 @@
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -4106,8 +4199,11 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4135,8 +4231,8 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4213,8 +4309,11 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4242,193 +4341,199 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
-      </c>
-      <c r="S45" s="3">
-        <v>800</v>
       </c>
       <c r="T45" s="3">
         <v>800</v>
       </c>
       <c r="U45" s="3">
+        <v>800</v>
+      </c>
+      <c r="V45" s="3">
         <v>1000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>600</v>
-      </c>
-      <c r="W45" s="3">
-        <v>800</v>
       </c>
       <c r="X45" s="3">
         <v>800</v>
       </c>
       <c r="Y45" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z45" s="3">
         <v>1500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>600</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>700</v>
       </c>
       <c r="AC45" s="3">
         <v>700</v>
       </c>
       <c r="AD45" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="AE45" s="3">
         <v>800</v>
       </c>
       <c r="AF45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AG45" s="3">
         <v>500</v>
-      </c>
-      <c r="AG45" s="3">
-        <v>1000</v>
       </c>
       <c r="AH45" s="3">
         <v>1000</v>
       </c>
       <c r="AI45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E46" s="3">
         <v>24300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>35900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>27900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>41400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>20100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>13800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>20500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>18800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>25300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>31400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>36600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>41400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>47100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>54400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>57900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>19800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>23000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>11400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>14800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>18200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>11100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>14000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>17100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>10500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>9300</v>
-      </c>
-      <c r="AI46" s="3">
-        <v>12200</v>
       </c>
       <c r="AJ46" s="3">
         <v>12200</v>
       </c>
       <c r="AK46" s="3">
+        <v>12200</v>
+      </c>
+      <c r="AL46" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4456,8 +4561,8 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4534,40 +4639,43 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1200</v>
-      </c>
-      <c r="E48" s="3">
-        <v>1400</v>
       </c>
       <c r="F48" s="3">
         <v>1400</v>
       </c>
       <c r="G48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H48" s="3">
         <v>1500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1400</v>
-      </c>
-      <c r="J48" s="3">
-        <v>900</v>
       </c>
       <c r="K48" s="3">
         <v>900</v>
       </c>
       <c r="L48" s="3">
+        <v>900</v>
+      </c>
+      <c r="M48" s="3">
         <v>1000</v>
-      </c>
-      <c r="M48" s="3">
-        <v>500</v>
       </c>
       <c r="N48" s="3">
         <v>500</v>
@@ -4585,13 +4693,13 @@
         <v>500</v>
       </c>
       <c r="S48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="T48" s="3">
         <v>600</v>
       </c>
       <c r="U48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="V48" s="3">
         <v>700</v>
@@ -4600,22 +4708,22 @@
         <v>700</v>
       </c>
       <c r="X48" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="Y48" s="3">
         <v>800</v>
       </c>
       <c r="Z48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AA48" s="3">
         <v>900</v>
       </c>
       <c r="AB48" s="3">
+        <v>900</v>
+      </c>
+      <c r="AC48" s="3">
         <v>500</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>200</v>
       </c>
       <c r="AD48" s="3">
         <v>200</v>
@@ -4627,22 +4735,25 @@
         <v>200</v>
       </c>
       <c r="AG48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH48" s="3">
         <v>1500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1600</v>
-      </c>
-      <c r="AI48" s="3">
-        <v>1400</v>
       </c>
       <c r="AJ48" s="3">
         <v>1400</v>
       </c>
       <c r="AK48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AL48" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4722,7 +4833,7 @@
         <v>0</v>
       </c>
       <c r="AC49" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="AD49" s="3">
         <v>1700</v>
@@ -4748,8 +4859,11 @@
       <c r="AK49" s="3">
         <v>1700</v>
       </c>
+      <c r="AL49" s="3">
+        <v>1700</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,8 +5079,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4989,7 +5109,7 @@
         <v>0</v>
       </c>
       <c r="K52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L52" s="3">
         <v>100</v>
@@ -5019,10 +5139,10 @@
         <v>100</v>
       </c>
       <c r="U52" s="3">
+        <v>100</v>
+      </c>
+      <c r="V52" s="3">
         <v>200</v>
-      </c>
-      <c r="V52" s="3">
-        <v>100</v>
       </c>
       <c r="W52" s="3">
         <v>100</v>
@@ -5037,26 +5157,26 @@
         <v>100</v>
       </c>
       <c r="AA52" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB52" s="3">
         <v>500</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>600</v>
       </c>
       <c r="AC52" s="3">
         <v>600</v>
       </c>
       <c r="AD52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE52" s="3">
         <v>100</v>
       </c>
-      <c r="AE52" s="3">
-        <v>0</v>
-      </c>
       <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3">
         <v>500</v>
       </c>
-      <c r="AG52" s="3">
-        <v>0</v>
-      </c>
       <c r="AH52" s="3">
         <v>0</v>
       </c>
@@ -5069,8 +5189,11 @@
       <c r="AK52" s="3">
         <v>0</v>
       </c>
+      <c r="AL52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E54" s="3">
         <v>25500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>37300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>29400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>42900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>19300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>25900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>32000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>37200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>42000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>47700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>55100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>58700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>20700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>23900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>8700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>12300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>15700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>19100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>15100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>19500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>9600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>12900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>9900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>12600</v>
-      </c>
-      <c r="AI54" s="3">
-        <v>15300</v>
       </c>
       <c r="AJ54" s="3">
         <v>15300</v>
       </c>
       <c r="AK54" s="3">
+        <v>15300</v>
+      </c>
+      <c r="AL54" s="3">
         <v>9300</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,115 +5491,119 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E57" s="3">
         <v>4100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2100</v>
-      </c>
-      <c r="AE57" s="3">
-        <v>1900</v>
       </c>
       <c r="AF57" s="3">
         <v>1900</v>
       </c>
       <c r="AG57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AH57" s="3">
         <v>2000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5498,7 +5632,7 @@
         <v>100</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -5570,42 +5704,45 @@
         <v>0</v>
       </c>
       <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="3">
         <v>100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E59" s="3">
         <v>1700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>21100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8600</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L59" s="3">
-        <v>100</v>
+      <c r="L59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M59" s="3">
         <v>100</v>
@@ -5659,7 +5796,7 @@
         <v>100</v>
       </c>
       <c r="AD59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AE59" s="3">
         <v>200</v>
@@ -5668,108 +5805,111 @@
         <v>200</v>
       </c>
       <c r="AG59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AH59" s="3">
         <v>100</v>
       </c>
       <c r="AI59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E60" s="3">
         <v>9400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>28600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>25400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>16500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2300</v>
-      </c>
-      <c r="AE60" s="3">
-        <v>2100</v>
       </c>
       <c r="AF60" s="3">
         <v>2100</v>
@@ -5778,19 +5918,22 @@
         <v>2100</v>
       </c>
       <c r="AH60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AI60" s="3">
         <v>1600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5801,7 +5944,7 @@
         <v>400</v>
       </c>
       <c r="F61" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G61" s="3">
         <v>500</v>
@@ -5819,7 +5962,7 @@
         <v>500</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -5846,13 +5989,13 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V61" s="3">
         <v>200</v>
       </c>
       <c r="W61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="X61" s="3">
         <v>0</v>
@@ -5896,13 +6039,16 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>4</v>
+      <c r="D62" s="3">
+        <v>1400</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>4</v>
@@ -5925,11 +6071,11 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>600</v>
-      </c>
-      <c r="M62" s="3">
-        <v>100</v>
       </c>
       <c r="N62" s="3">
         <v>100</v>
@@ -5938,7 +6084,7 @@
         <v>100</v>
       </c>
       <c r="P62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q62" s="3">
         <v>200</v>
@@ -5947,7 +6093,7 @@
         <v>200</v>
       </c>
       <c r="S62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="T62" s="3">
         <v>300</v>
@@ -5956,7 +6102,7 @@
         <v>300</v>
       </c>
       <c r="V62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="W62" s="3">
         <v>400</v>
@@ -5968,28 +6114,28 @@
         <v>400</v>
       </c>
       <c r="Z62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AA62" s="3">
         <v>500</v>
       </c>
       <c r="AB62" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC62" s="3">
         <v>200</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF62" s="3">
-        <v>0</v>
+      <c r="AF62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH62" s="3">
         <v>100</v>
@@ -6003,8 +6149,11 @@
       <c r="AK62" s="3">
         <v>100</v>
       </c>
+      <c r="AL62" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E66" s="3">
         <v>9800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>20700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>15600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>29000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>25900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>17000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2300</v>
-      </c>
-      <c r="AE66" s="3">
-        <v>2100</v>
       </c>
       <c r="AF66" s="3">
         <v>2100</v>
       </c>
       <c r="AG66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AH66" s="3">
         <v>2300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,31 +6849,34 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>500</v>
+      </c>
+      <c r="E70" s="3">
         <v>1900</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>15000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>9200</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>18400</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>6100</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>19300</v>
-      </c>
-      <c r="J70" s="3">
-        <v>1400</v>
       </c>
       <c r="K70" s="3">
         <v>1400</v>
@@ -6732,16 +6900,16 @@
         <v>1400</v>
       </c>
       <c r="R70" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S70" s="3">
         <v>8600</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>11700</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>20000</v>
-      </c>
-      <c r="U70" s="3">
-        <v>1100</v>
       </c>
       <c r="V70" s="3">
         <v>1100</v>
@@ -6759,26 +6927,26 @@
         <v>1100</v>
       </c>
       <c r="AA70" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB70" s="3">
         <v>1800</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>2500</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>3500</v>
       </c>
-      <c r="AD70" s="3">
-        <v>0</v>
-      </c>
       <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3">
         <v>600</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>1000</v>
       </c>
-      <c r="AG70" s="3">
-        <v>0</v>
-      </c>
       <c r="AH70" s="3">
         <v>0</v>
       </c>
@@ -6786,13 +6954,16 @@
         <v>0</v>
       </c>
       <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
         <v>900</v>
       </c>
-      <c r="AK70" s="3">
+      <c r="AL70" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-253900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-247300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-245000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-230300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-229400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-202800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-210000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-196300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-188100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-179500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-172300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-164500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-157000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-150900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-145000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-139200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-133100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-126800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-123200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-119300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-115600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-111700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-108300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-104400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-101200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-97600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-93800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-90700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-87800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-84300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-80300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-76800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-73700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-70800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-68200</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E76" s="3">
         <v>13800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-4600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-19800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-14700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>25800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>31700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>37200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>35300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>38000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>34800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>18800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>10700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>9800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>10900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>13700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-14700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-26600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-17500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10200</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-7200</v>
       </c>
       <c r="L81" s="3">
         <v>-7200</v>
       </c>
       <c r="M81" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="N81" s="3">
         <v>-7800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-6000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-5300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-5500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,8 +7996,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7807,7 +8006,7 @@
         <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -7888,10 +8087,10 @@
         <v>0</v>
       </c>
       <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3">
         <v>1300</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>100</v>
       </c>
       <c r="AH83" s="3">
         <v>100</v>
@@ -7905,8 +8104,11 @@
       <c r="AK83" s="3">
         <v>100</v>
       </c>
+      <c r="AL83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-10900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-9200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-14100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-13400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-9600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-6900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-3500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,17 +8806,18 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
@@ -8604,43 +8825,43 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-600</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>4</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -8664,11 +8885,11 @@
         <v>0</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-400</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
@@ -8682,19 +8903,22 @@
         <v>0</v>
       </c>
       <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AI91" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ91" s="3">
         <v>-100</v>
       </c>
       <c r="AK91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,17 +9134,20 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
@@ -8925,43 +9155,43 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-600</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -8985,11 +9215,11 @@
         <v>0</v>
       </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-400</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
       <c r="AD94" s="3">
         <v>0</v>
       </c>
@@ -9003,19 +9233,22 @@
         <v>0</v>
       </c>
       <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-300</v>
-      </c>
-      <c r="AI94" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ94" s="3">
         <v>-100</v>
       </c>
       <c r="AK94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9082,8 +9316,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9160,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,41 +9724,44 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>17600</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>43800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>22500</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>9600</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
@@ -9532,20 +9778,20 @@
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>1200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>42200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>18400</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
@@ -9553,43 +9799,46 @@
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>9000</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>15100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-100</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>7200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-100</v>
       </c>
-      <c r="AH100" s="3">
-        <v>0</v>
-      </c>
       <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>8200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9617,8 +9866,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9695,111 +9944,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>8400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-14200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>30500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>13800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-6800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>38300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>15400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>6400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>12200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>4300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>5800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-2300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CLRB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CLRB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
   <si>
     <t>CLRB</t>
   </si>
@@ -656,162 +656,166 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -842,8 +846,8 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -920,8 +924,11 @@
       <c r="AL8" s="3">
         <v>0</v>
       </c>
+      <c r="AM8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1030,8 +1037,11 @@
       <c r="AL9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1140,8 +1150,11 @@
       <c r="AL10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1180,118 +1193,122 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E12" s="3">
         <v>3400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>7100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3900</v>
-      </c>
-      <c r="S12" s="3">
-        <v>4600</v>
       </c>
       <c r="T12" s="3">
         <v>4600</v>
       </c>
       <c r="U12" s="3">
+        <v>4600</v>
+      </c>
+      <c r="V12" s="3">
         <v>2400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>2200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>2700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>2300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>2000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>2100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>3100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>2300</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1900</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>1400</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,8 +1417,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1432,23 +1452,23 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>4</v>
@@ -1456,23 +1476,23 @@
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V14" s="3">
         <v>-200</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>4</v>
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>4</v>
@@ -1480,12 +1500,12 @@
       <c r="AB14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD14" s="3">
         <v>1700</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1504,14 +1524,17 @@
       <c r="AJ14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
+      <c r="AK14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1534,7 +1557,7 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E17" s="3">
         <v>6400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>12700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-6400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-12000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-12500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-9400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-6000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-6400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,44 +1950,45 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-10200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-12500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>15000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>8200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1989,22 +2023,22 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
       <c r="AC20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD20" s="3">
         <v>100</v>
       </c>
       <c r="AE20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF20" s="3">
         <v>0</v>
@@ -2016,129 +2050,135 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-14900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-26900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-8000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-17500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-10200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-7300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-7800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-5900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-5800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-6000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-6300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-3400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-2800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2169,8 +2209,8 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2247,154 +2287,160 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-14700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-26600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-17500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-3100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G24" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2410,8 +2456,8 @@
       <c r="S24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -2467,8 +2513,11 @@
       <c r="AL24" s="3">
         <v>0</v>
       </c>
+      <c r="AM24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-14700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-26600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-17500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10200</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-7200</v>
       </c>
       <c r="M26" s="3">
         <v>-7200</v>
       </c>
       <c r="N26" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="O26" s="3">
         <v>-7800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-6400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-14700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-26600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-17500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10200</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-7200</v>
       </c>
       <c r="M27" s="3">
         <v>-7200</v>
       </c>
       <c r="N27" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="O27" s="3">
         <v>-7800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-5300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-5500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,44 +3304,47 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>10200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>12500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-15000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-8200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -3309,22 +3379,22 @@
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
       <c r="AC32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD32" s="3">
         <v>-100</v>
       </c>
       <c r="AE32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AF32" s="3">
         <v>0</v>
@@ -3336,129 +3406,135 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-14700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-26600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-17500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10200</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-7200</v>
       </c>
       <c r="M33" s="3">
         <v>-7200</v>
       </c>
       <c r="N33" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="O33" s="3">
         <v>-7800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-5300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-5500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-14700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-26600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-17500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10200</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-7200</v>
       </c>
       <c r="M35" s="3">
         <v>-7200</v>
       </c>
       <c r="N35" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="O35" s="3">
         <v>-7800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-5300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-5500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,118 +3958,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E41" s="3">
         <v>13900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>23300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>34300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>25900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>40000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>19000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>19900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>24800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>30600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>35700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>40300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>46800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>53600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>57200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>18800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>22500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>10600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>13300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>16800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>10500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>13300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>16400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>10000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>8300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>11200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>11400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4092,8 +4182,11 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4124,8 +4217,8 @@
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -4202,8 +4295,11 @@
       <c r="AL43" s="3">
         <v>0</v>
       </c>
+      <c r="AM43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4234,8 +4330,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4312,8 +4408,11 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4344,196 +4443,202 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>300</v>
-      </c>
-      <c r="T45" s="3">
-        <v>800</v>
       </c>
       <c r="U45" s="3">
         <v>800</v>
       </c>
       <c r="V45" s="3">
+        <v>800</v>
+      </c>
+      <c r="W45" s="3">
         <v>1000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>600</v>
-      </c>
-      <c r="X45" s="3">
-        <v>800</v>
       </c>
       <c r="Y45" s="3">
         <v>800</v>
       </c>
       <c r="Z45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA45" s="3">
         <v>1500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>600</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>700</v>
       </c>
       <c r="AD45" s="3">
         <v>700</v>
       </c>
       <c r="AE45" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="AF45" s="3">
         <v>800</v>
       </c>
       <c r="AG45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AH45" s="3">
         <v>500</v>
-      </c>
-      <c r="AH45" s="3">
-        <v>1000</v>
       </c>
       <c r="AI45" s="3">
         <v>1000</v>
       </c>
       <c r="AJ45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AK45" s="3">
         <v>900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E46" s="3">
         <v>14900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>24300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>35900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>27900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>41400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>20100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>20500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>25300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>31400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>36600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>41400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>47100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>54400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>57900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>19800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>23000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>11400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>14800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>18200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>11100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>14000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>17100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>10500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>9300</v>
-      </c>
-      <c r="AJ46" s="3">
-        <v>12200</v>
       </c>
       <c r="AK46" s="3">
         <v>12200</v>
       </c>
       <c r="AL46" s="3">
+        <v>12200</v>
+      </c>
+      <c r="AM46" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4564,8 +4669,8 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4642,43 +4747,46 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1200</v>
-      </c>
-      <c r="F48" s="3">
-        <v>1400</v>
       </c>
       <c r="G48" s="3">
         <v>1400</v>
       </c>
       <c r="H48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I48" s="3">
         <v>1500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1400</v>
-      </c>
-      <c r="K48" s="3">
-        <v>900</v>
       </c>
       <c r="L48" s="3">
         <v>900</v>
       </c>
       <c r="M48" s="3">
+        <v>900</v>
+      </c>
+      <c r="N48" s="3">
         <v>1000</v>
-      </c>
-      <c r="N48" s="3">
-        <v>500</v>
       </c>
       <c r="O48" s="3">
         <v>500</v>
@@ -4696,13 +4804,13 @@
         <v>500</v>
       </c>
       <c r="T48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="U48" s="3">
         <v>600</v>
       </c>
       <c r="V48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="W48" s="3">
         <v>700</v>
@@ -4711,22 +4819,22 @@
         <v>700</v>
       </c>
       <c r="Y48" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="Z48" s="3">
         <v>800</v>
       </c>
       <c r="AA48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AB48" s="3">
         <v>900</v>
       </c>
       <c r="AC48" s="3">
+        <v>900</v>
+      </c>
+      <c r="AD48" s="3">
         <v>500</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>200</v>
       </c>
       <c r="AE48" s="3">
         <v>200</v>
@@ -4738,22 +4846,25 @@
         <v>200</v>
       </c>
       <c r="AH48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI48" s="3">
         <v>1500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1600</v>
-      </c>
-      <c r="AJ48" s="3">
-        <v>1400</v>
       </c>
       <c r="AK48" s="3">
         <v>1400</v>
       </c>
       <c r="AL48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AM48" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4836,7 +4947,7 @@
         <v>0</v>
       </c>
       <c r="AD49" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="AE49" s="3">
         <v>1700</v>
@@ -4862,8 +4973,11 @@
       <c r="AL49" s="3">
         <v>1700</v>
       </c>
+      <c r="AM49" s="3">
+        <v>1700</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,8 +5199,11 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5112,7 +5232,7 @@
         <v>0</v>
       </c>
       <c r="L52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M52" s="3">
         <v>100</v>
@@ -5142,10 +5262,10 @@
         <v>100</v>
       </c>
       <c r="V52" s="3">
+        <v>100</v>
+      </c>
+      <c r="W52" s="3">
         <v>200</v>
-      </c>
-      <c r="W52" s="3">
-        <v>100</v>
       </c>
       <c r="X52" s="3">
         <v>100</v>
@@ -5160,26 +5280,26 @@
         <v>100</v>
       </c>
       <c r="AB52" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC52" s="3">
         <v>500</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>600</v>
       </c>
       <c r="AD52" s="3">
         <v>600</v>
       </c>
       <c r="AE52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF52" s="3">
         <v>100</v>
       </c>
-      <c r="AF52" s="3">
-        <v>0</v>
-      </c>
       <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3">
         <v>500</v>
       </c>
-      <c r="AH52" s="3">
-        <v>0</v>
-      </c>
       <c r="AI52" s="3">
         <v>0</v>
       </c>
@@ -5192,8 +5312,11 @@
       <c r="AL52" s="3">
         <v>0</v>
       </c>
+      <c r="AM52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E54" s="3">
         <v>16000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>25500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>37300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>29400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>42900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>19300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>25900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>32000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>37200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>42000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>47700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>55100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>58700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>20700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>23900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>8700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>12300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>15700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>19100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>15100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>19500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>9600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>9900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>12600</v>
-      </c>
-      <c r="AJ54" s="3">
-        <v>15300</v>
       </c>
       <c r="AK54" s="3">
         <v>15300</v>
       </c>
       <c r="AL54" s="3">
+        <v>15300</v>
+      </c>
+      <c r="AM54" s="3">
         <v>9300</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,118 +5622,122 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E57" s="3">
         <v>3900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2100</v>
-      </c>
-      <c r="AF57" s="3">
-        <v>1900</v>
       </c>
       <c r="AG57" s="3">
         <v>1900</v>
       </c>
       <c r="AH57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AI57" s="3">
         <v>2000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5635,7 +5769,7 @@
         <v>100</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -5707,45 +5841,48 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="3">
         <v>100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E59" s="3">
         <v>2100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>21100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8600</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M59" s="3">
-        <v>100</v>
+      <c r="M59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N59" s="3">
         <v>100</v>
@@ -5799,7 +5936,7 @@
         <v>100</v>
       </c>
       <c r="AE59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AF59" s="3">
         <v>200</v>
@@ -5808,111 +5945,114 @@
         <v>200</v>
       </c>
       <c r="AH59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AI59" s="3">
         <v>100</v>
       </c>
       <c r="AJ59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK59" s="3">
         <v>200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E60" s="3">
         <v>6000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>28600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>25400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>16500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2300</v>
-      </c>
-      <c r="AF60" s="3">
-        <v>2100</v>
       </c>
       <c r="AG60" s="3">
         <v>2100</v>
@@ -5921,19 +6061,22 @@
         <v>2100</v>
       </c>
       <c r="AI60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AJ60" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5947,7 +6090,7 @@
         <v>400</v>
       </c>
       <c r="G61" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H61" s="3">
         <v>500</v>
@@ -5965,7 +6108,7 @@
         <v>500</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
@@ -5992,13 +6135,13 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="W61" s="3">
         <v>200</v>
       </c>
       <c r="X61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Y61" s="3">
         <v>0</v>
@@ -6042,13 +6185,16 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>1400</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>4</v>
@@ -6074,11 +6220,11 @@
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>600</v>
-      </c>
-      <c r="N62" s="3">
-        <v>100</v>
       </c>
       <c r="O62" s="3">
         <v>100</v>
@@ -6087,7 +6233,7 @@
         <v>100</v>
       </c>
       <c r="Q62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R62" s="3">
         <v>200</v>
@@ -6096,7 +6242,7 @@
         <v>200</v>
       </c>
       <c r="T62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U62" s="3">
         <v>300</v>
@@ -6105,7 +6251,7 @@
         <v>300</v>
       </c>
       <c r="W62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="X62" s="3">
         <v>400</v>
@@ -6117,28 +6263,28 @@
         <v>400</v>
       </c>
       <c r="AA62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AB62" s="3">
         <v>500</v>
       </c>
       <c r="AC62" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD62" s="3">
         <v>200</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG62" s="3">
-        <v>0</v>
+      <c r="AG62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI62" s="3">
         <v>100</v>
@@ -6152,8 +6298,11 @@
       <c r="AL62" s="3">
         <v>100</v>
       </c>
+      <c r="AM62" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>7800</v>
+        <v>6200</v>
       </c>
       <c r="E66" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F66" s="3">
         <v>9800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>20700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>29000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>25900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>17000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2300</v>
-      </c>
-      <c r="AF66" s="3">
-        <v>2100</v>
       </c>
       <c r="AG66" s="3">
         <v>2100</v>
       </c>
       <c r="AH66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AI66" s="3">
         <v>2300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,34 +7017,37 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>500</v>
+        <v>1900</v>
       </c>
       <c r="E70" s="3">
         <v>1900</v>
       </c>
       <c r="F70" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G70" s="3">
         <v>15000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>9200</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>18400</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>6100</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>19300</v>
-      </c>
-      <c r="K70" s="3">
-        <v>1400</v>
       </c>
       <c r="L70" s="3">
         <v>1400</v>
@@ -6903,16 +7071,16 @@
         <v>1400</v>
       </c>
       <c r="S70" s="3">
+        <v>1400</v>
+      </c>
+      <c r="T70" s="3">
         <v>8600</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>11700</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>20000</v>
-      </c>
-      <c r="V70" s="3">
-        <v>1100</v>
       </c>
       <c r="W70" s="3">
         <v>1100</v>
@@ -6930,26 +7098,26 @@
         <v>1100</v>
       </c>
       <c r="AB70" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC70" s="3">
         <v>1800</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>2500</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>3500</v>
       </c>
-      <c r="AE70" s="3">
-        <v>0</v>
-      </c>
       <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
         <v>600</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>1000</v>
       </c>
-      <c r="AH70" s="3">
-        <v>0</v>
-      </c>
       <c r="AI70" s="3">
         <v>0</v>
       </c>
@@ -6957,13 +7125,16 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="3">
         <v>900</v>
       </c>
-      <c r="AL70" s="3">
+      <c r="AM70" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-259400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-253900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-247300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-245000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-230300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-229400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-202800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-210000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-196300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-188100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-179500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-172300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-164500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-157000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-150900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-145000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-139200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-133100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-126800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-123200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-119300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-115600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-111700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-108300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-104400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-101200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-97600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-93800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-90700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-87800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-84300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-80300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-76800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-73700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-70800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-68200</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E76" s="3">
         <v>7700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-4600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-19800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-14700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>25800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>31700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>37200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>35300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>38000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>34800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>18800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>10700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>9800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>7600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>10900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>13700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>12700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-14700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-26600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-17500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10200</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-7200</v>
       </c>
       <c r="M81" s="3">
         <v>-7200</v>
       </c>
       <c r="N81" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="O81" s="3">
         <v>-7800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-5300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-5500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,8 +8195,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8009,7 +8208,7 @@
         <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
         <v>0</v>
@@ -8090,10 +8289,10 @@
         <v>0</v>
       </c>
       <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3">
         <v>1300</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>100</v>
       </c>
       <c r="AI83" s="3">
         <v>100</v>
@@ -8107,8 +8306,11 @@
       <c r="AL83" s="3">
         <v>100</v>
       </c>
+      <c r="AM83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-9400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-10900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-9200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-14100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-13400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-9600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-8100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-6400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-6900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-3000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,20 +9027,21 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E91" s="3">
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
@@ -8828,43 +9049,43 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-600</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>4</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -8888,11 +9109,11 @@
         <v>0</v>
       </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-400</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
-      </c>
       <c r="AE91" s="3">
         <v>0</v>
       </c>
@@ -8906,19 +9127,22 @@
         <v>0</v>
       </c>
       <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AJ91" s="3">
-        <v>-100</v>
       </c>
       <c r="AK91" s="3">
         <v>-100</v>
       </c>
       <c r="AL91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,20 +9364,23 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E94" s="3">
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
@@ -9158,43 +9388,43 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-600</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>4</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -9218,11 +9448,11 @@
         <v>0</v>
       </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-400</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
       <c r="AE94" s="3">
         <v>0</v>
       </c>
@@ -9236,19 +9466,22 @@
         <v>0</v>
       </c>
       <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-300</v>
-      </c>
-      <c r="AJ94" s="3">
-        <v>-100</v>
       </c>
       <c r="AK94" s="3">
         <v>-100</v>
       </c>
       <c r="AL94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9319,8 +9553,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,44 +9970,47 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
+      <c r="D100" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>17600</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>43800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>22500</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>9600</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
@@ -9781,20 +10027,20 @@
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>1200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>42200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>18400</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
@@ -9802,43 +10048,46 @@
         <v>0</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>9000</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
         <v>0</v>
       </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>15100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-100</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>7200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-100</v>
       </c>
-      <c r="AI100" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK100" s="3">
         <v>2800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>8200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9869,8 +10118,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9947,114 +10196,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-14200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>30500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>13800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-6400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>38300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>15400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>6400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>12200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>4300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>5800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-2300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CLRB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CLRB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
   <si>
     <t>CLRB</t>
   </si>
@@ -656,170 +656,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -856,8 +859,8 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -934,8 +937,11 @@
       <c r="AN8" s="3">
         <v>0</v>
       </c>
+      <c r="AO8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1050,8 +1056,11 @@
       <c r="AN9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1175,11 @@
       <c r="AN10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1208,124 +1220,128 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E12" s="3">
         <v>2500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>4400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3900</v>
-      </c>
-      <c r="U12" s="3">
-        <v>4600</v>
       </c>
       <c r="V12" s="3">
         <v>4600</v>
       </c>
       <c r="W12" s="3">
+        <v>4600</v>
+      </c>
+      <c r="X12" s="3">
         <v>2400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>2500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>2600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>2200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>2700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>2300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>2000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1700</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>2100</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>2300</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>2200</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>1900</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>1400</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,8 +1456,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1478,23 +1497,23 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>4</v>
@@ -1502,23 +1521,23 @@
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X14" s="3">
         <v>-200</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>4</v>
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>4</v>
@@ -1526,12 +1545,12 @@
       <c r="AD14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF14" s="3">
         <v>1700</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1550,19 +1569,22 @@
       <c r="AL14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AM14" s="3">
-        <v>0</v>
+      <c r="AM14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>100</v>
@@ -1586,7 +1608,7 @@
         <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1672,8 +1694,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1736,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E17" s="3">
         <v>4900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-6000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-6400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-12700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-12000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-12500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-7400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-6000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-6400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-4100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,8 +2017,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1994,41 +2027,41 @@
         <v>-300</v>
       </c>
       <c r="E20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F20" s="3">
         <v>-500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-10200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-12500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>15000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -2063,22 +2096,22 @@
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
       <c r="AE20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF20" s="3">
         <v>100</v>
       </c>
       <c r="AG20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH20" s="3">
         <v>0</v>
@@ -2090,135 +2123,141 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="3">
         <v>100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-4500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-5500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-14900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-26900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-17500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-10200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-7300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-7400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-6100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-5900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-6000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-6300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-2800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-3400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-2800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2255,8 +2294,8 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2333,124 +2372,130 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-14700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-26600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-17500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-10200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-3100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2463,36 +2508,36 @@
       <c r="F24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2508,8 +2553,8 @@
       <c r="U24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="V24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -2565,8 +2610,11 @@
       <c r="AN24" s="3">
         <v>0</v>
       </c>
+      <c r="AO24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2729,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-14700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-26600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-17500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-10200</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-7200</v>
       </c>
       <c r="O26" s="3">
         <v>-7200</v>
       </c>
       <c r="P26" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-6000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-6400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-2600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-14700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-26600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-17500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-10200</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-7200</v>
       </c>
       <c r="O27" s="3">
         <v>-7200</v>
       </c>
       <c r="P27" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-6000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-6400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-5300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-5500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3086,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3145,8 +3205,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3324,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,8 +3443,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3386,41 +3455,41 @@
         <v>300</v>
       </c>
       <c r="E32" s="3">
+        <v>300</v>
+      </c>
+      <c r="F32" s="3">
         <v>500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>10200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>12500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-15000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -3455,22 +3524,22 @@
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
       <c r="AE32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF32" s="3">
         <v>-100</v>
       </c>
       <c r="AG32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AH32" s="3">
         <v>0</v>
@@ -3482,135 +3551,141 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="3">
         <v>-100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-14700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-26600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-17500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-10200</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-7200</v>
       </c>
       <c r="O33" s="3">
         <v>-7200</v>
       </c>
       <c r="P33" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-6100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-6000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-6400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-5300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-5500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3800,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-14700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-26600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-17500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-10200</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-7200</v>
       </c>
       <c r="O35" s="3">
         <v>-7200</v>
       </c>
       <c r="P35" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-6100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-6000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-6400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-5300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-5500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4088,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,124 +4131,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E41" s="3">
         <v>12600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>13900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>23300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>34300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>25900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>40000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>19000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>19900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>17800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>24800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>30600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>35700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>40300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>46800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>53600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>57200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>18800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>22500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>10600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>13300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>16800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>10500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>13300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>16400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>10000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>5700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>8300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>11200</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>11400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4278,8 +4367,11 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4316,8 +4408,8 @@
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -4394,8 +4486,11 @@
       <c r="AN43" s="3">
         <v>0</v>
       </c>
+      <c r="AO43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4432,8 +4527,8 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4510,8 +4605,11 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4548,202 +4646,208 @@
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3">
         <v>700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>300</v>
-      </c>
-      <c r="V45" s="3">
-        <v>800</v>
       </c>
       <c r="W45" s="3">
         <v>800</v>
       </c>
       <c r="X45" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y45" s="3">
         <v>1000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>600</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>800</v>
       </c>
       <c r="AA45" s="3">
         <v>800</v>
       </c>
       <c r="AB45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC45" s="3">
         <v>1500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>600</v>
-      </c>
-      <c r="AE45" s="3">
-        <v>700</v>
       </c>
       <c r="AF45" s="3">
         <v>700</v>
       </c>
       <c r="AG45" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="AH45" s="3">
         <v>800</v>
       </c>
       <c r="AI45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>500</v>
-      </c>
-      <c r="AJ45" s="3">
-        <v>1000</v>
       </c>
       <c r="AK45" s="3">
         <v>1000</v>
       </c>
       <c r="AL45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AM45" s="3">
         <v>900</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>700</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E46" s="3">
         <v>13600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>24300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>35900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>27900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>41400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>20100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>20500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>18800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>25300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>31400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>36600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>41400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>47100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>54400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>57900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>19800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>23000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>11400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>14800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>18200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>11100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>14000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>17100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>10500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>6700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>9300</v>
-      </c>
-      <c r="AL46" s="3">
-        <v>12200</v>
       </c>
       <c r="AM46" s="3">
         <v>12200</v>
       </c>
       <c r="AN46" s="3">
+        <v>12200</v>
+      </c>
+      <c r="AO46" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4780,8 +4884,8 @@
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4858,49 +4962,52 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E48" s="3">
         <v>1000</v>
       </c>
       <c r="F48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G48" s="3">
         <v>1100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1200</v>
-      </c>
-      <c r="H48" s="3">
-        <v>1400</v>
       </c>
       <c r="I48" s="3">
         <v>1400</v>
       </c>
       <c r="J48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K48" s="3">
         <v>1500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1400</v>
-      </c>
-      <c r="M48" s="3">
-        <v>900</v>
       </c>
       <c r="N48" s="3">
         <v>900</v>
       </c>
       <c r="O48" s="3">
+        <v>900</v>
+      </c>
+      <c r="P48" s="3">
         <v>1000</v>
-      </c>
-      <c r="P48" s="3">
-        <v>500</v>
       </c>
       <c r="Q48" s="3">
         <v>500</v>
@@ -4918,13 +5025,13 @@
         <v>500</v>
       </c>
       <c r="V48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W48" s="3">
         <v>600</v>
       </c>
       <c r="X48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="Y48" s="3">
         <v>700</v>
@@ -4933,22 +5040,22 @@
         <v>700</v>
       </c>
       <c r="AA48" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="AB48" s="3">
         <v>800</v>
       </c>
       <c r="AC48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AD48" s="3">
         <v>900</v>
       </c>
       <c r="AE48" s="3">
+        <v>900</v>
+      </c>
+      <c r="AF48" s="3">
         <v>500</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>200</v>
       </c>
       <c r="AG48" s="3">
         <v>200</v>
@@ -4960,22 +5067,25 @@
         <v>200</v>
       </c>
       <c r="AJ48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AK48" s="3">
         <v>1500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1600</v>
-      </c>
-      <c r="AL48" s="3">
-        <v>1400</v>
       </c>
       <c r="AM48" s="3">
         <v>1400</v>
       </c>
       <c r="AN48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AO48" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5064,7 +5174,7 @@
         <v>0</v>
       </c>
       <c r="AF49" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="AG49" s="3">
         <v>1700</v>
@@ -5090,8 +5200,11 @@
       <c r="AN49" s="3">
         <v>1700</v>
       </c>
+      <c r="AO49" s="3">
+        <v>1700</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5319,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,8 +5438,11 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5358,7 +5477,7 @@
         <v>0</v>
       </c>
       <c r="N52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O52" s="3">
         <v>100</v>
@@ -5388,10 +5507,10 @@
         <v>100</v>
       </c>
       <c r="X52" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y52" s="3">
         <v>200</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>100</v>
       </c>
       <c r="Z52" s="3">
         <v>100</v>
@@ -5406,26 +5525,26 @@
         <v>100</v>
       </c>
       <c r="AD52" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE52" s="3">
         <v>500</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>600</v>
       </c>
       <c r="AF52" s="3">
         <v>600</v>
       </c>
       <c r="AG52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AH52" s="3">
         <v>100</v>
       </c>
-      <c r="AH52" s="3">
-        <v>0</v>
-      </c>
       <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>500</v>
       </c>
-      <c r="AJ52" s="3">
-        <v>0</v>
-      </c>
       <c r="AK52" s="3">
         <v>0</v>
       </c>
@@ -5438,8 +5557,11 @@
       <c r="AN52" s="3">
         <v>0</v>
       </c>
+      <c r="AO52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5676,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E54" s="3">
         <v>14600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>25500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>37300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>29400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>42900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>19300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>25900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>32000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>37200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>42000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>47700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>55100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>58700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>20700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>23900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>8700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>15700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>19100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>12500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>15100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>19500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>9600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>12900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>9900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>12600</v>
-      </c>
-      <c r="AL54" s="3">
-        <v>15300</v>
       </c>
       <c r="AM54" s="3">
         <v>15300</v>
       </c>
       <c r="AN54" s="3">
+        <v>15300</v>
+      </c>
+      <c r="AO54" s="3">
         <v>9300</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5840,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,124 +5883,128 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E57" s="3">
         <v>4000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2100</v>
-      </c>
-      <c r="AH57" s="3">
-        <v>1900</v>
       </c>
       <c r="AI57" s="3">
         <v>1900</v>
       </c>
       <c r="AJ57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AK57" s="3">
         <v>2000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5909,7 +6042,7 @@
         <v>100</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -5981,51 +6114,54 @@
         <v>0</v>
       </c>
       <c r="AM58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="3">
         <v>100</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>700</v>
+      </c>
+      <c r="E59" s="3">
         <v>800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2100</v>
       </c>
-      <c r="G59" s="3">
-        <v>1700</v>
-      </c>
       <c r="H59" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I59" s="3">
         <v>11900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>21100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8600</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O59" s="3">
-        <v>100</v>
+      <c r="O59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P59" s="3">
         <v>100</v>
@@ -6079,7 +6215,7 @@
         <v>100</v>
       </c>
       <c r="AG59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AH59" s="3">
         <v>200</v>
@@ -6088,117 +6224,120 @@
         <v>200</v>
       </c>
       <c r="AJ59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AK59" s="3">
         <v>100</v>
       </c>
       <c r="AL59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM59" s="3">
         <v>200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E60" s="3">
         <v>4900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>20300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>28600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>25400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>16500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2300</v>
-      </c>
-      <c r="AH60" s="3">
-        <v>2100</v>
       </c>
       <c r="AI60" s="3">
         <v>2100</v>
@@ -6207,19 +6346,22 @@
         <v>2100</v>
       </c>
       <c r="AK60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AL60" s="3">
         <v>1600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1600</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -6227,7 +6369,7 @@
         <v>300</v>
       </c>
       <c r="E61" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F61" s="3">
         <v>400</v>
@@ -6239,7 +6381,7 @@
         <v>400</v>
       </c>
       <c r="I61" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J61" s="3">
         <v>500</v>
@@ -6257,7 +6399,7 @@
         <v>500</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
@@ -6284,13 +6426,13 @@
         <v>0</v>
       </c>
       <c r="X61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Y61" s="3">
         <v>200</v>
       </c>
       <c r="Z61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AA61" s="3">
         <v>0</v>
@@ -6334,8 +6476,11 @@
       <c r="AN61" s="3">
         <v>0</v>
       </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6372,11 +6517,11 @@
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3">
         <v>600</v>
-      </c>
-      <c r="P62" s="3">
-        <v>100</v>
       </c>
       <c r="Q62" s="3">
         <v>100</v>
@@ -6385,7 +6530,7 @@
         <v>100</v>
       </c>
       <c r="S62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T62" s="3">
         <v>200</v>
@@ -6394,7 +6539,7 @@
         <v>200</v>
       </c>
       <c r="V62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="W62" s="3">
         <v>300</v>
@@ -6403,7 +6548,7 @@
         <v>300</v>
       </c>
       <c r="Y62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Z62" s="3">
         <v>400</v>
@@ -6415,28 +6560,28 @@
         <v>400</v>
       </c>
       <c r="AC62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AD62" s="3">
         <v>500</v>
       </c>
       <c r="AE62" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF62" s="3">
         <v>200</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AH62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI62" s="3">
-        <v>0</v>
+      <c r="AI62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AK62" s="3">
         <v>100</v>
@@ -6450,8 +6595,11 @@
       <c r="AN62" s="3">
         <v>100</v>
       </c>
+      <c r="AO62" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6714,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6833,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +6952,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E66" s="3">
         <v>5200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>20700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>29000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>17000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2300</v>
-      </c>
-      <c r="AH66" s="3">
-        <v>2100</v>
       </c>
       <c r="AI66" s="3">
         <v>2100</v>
       </c>
       <c r="AJ66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AK66" s="3">
         <v>2300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7116,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7233,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7352,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7206,22 +7373,22 @@
         <v>1900</v>
       </c>
       <c r="H70" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I70" s="3">
         <v>15000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>9200</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>18400</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>6100</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>19300</v>
-      </c>
-      <c r="M70" s="3">
-        <v>1400</v>
       </c>
       <c r="N70" s="3">
         <v>1400</v>
@@ -7245,16 +7412,16 @@
         <v>1400</v>
       </c>
       <c r="U70" s="3">
+        <v>1400</v>
+      </c>
+      <c r="V70" s="3">
         <v>8600</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>11700</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>20000</v>
-      </c>
-      <c r="X70" s="3">
-        <v>1100</v>
       </c>
       <c r="Y70" s="3">
         <v>1100</v>
@@ -7272,26 +7439,26 @@
         <v>1100</v>
       </c>
       <c r="AD70" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AE70" s="3">
         <v>1800</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>2500</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>3500</v>
       </c>
-      <c r="AG70" s="3">
-        <v>0</v>
-      </c>
       <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
         <v>600</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AJ70" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ70" s="3">
-        <v>0</v>
-      </c>
       <c r="AK70" s="3">
         <v>0</v>
       </c>
@@ -7299,13 +7466,16 @@
         <v>0</v>
       </c>
       <c r="AM70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="3">
         <v>900</v>
       </c>
-      <c r="AN70" s="3">
+      <c r="AO70" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7590,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-269100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-263800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-259400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-253900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-247300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-245000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-230300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-229400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-202800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-210000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-196300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-188100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-179500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-172300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-164500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-157000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-150900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-145000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-139200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-133100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-126800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-123200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-119300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-115600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-111700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-108300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-104400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-101200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-97600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-93800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-90700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-87800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-84300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-80300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-76800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-73700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-70800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-68200</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +7828,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +7947,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8066,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-4600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-19800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-14700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-1800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>18800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>25800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>31700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>37200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>35300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>38000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>34800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>18800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>10700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>13400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>9800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>7600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>10900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>13700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>12700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8304,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-14700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-26600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-17500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-10200</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-7200</v>
       </c>
       <c r="O81" s="3">
         <v>-7200</v>
       </c>
       <c r="P81" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-6100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-6000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-6400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-5300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-5500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,8 +8592,9 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8413,7 +8611,7 @@
         <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
         <v>0</v>
@@ -8494,10 +8692,10 @@
         <v>0</v>
       </c>
       <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>1300</v>
-      </c>
-      <c r="AJ83" s="3">
-        <v>100</v>
       </c>
       <c r="AK83" s="3">
         <v>100</v>
@@ -8511,8 +8709,11 @@
       <c r="AN83" s="3">
         <v>100</v>
       </c>
+      <c r="AO83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +8828,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +8947,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9066,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9185,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,8 +9304,11 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -9100,115 +9316,118 @@
         <v>-4300</v>
       </c>
       <c r="E89" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-5100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-9400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-10900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-9200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-14100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-13400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-5000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-6400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-6900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-3900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-3200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,13 +9468,14 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>4</v>
+      <c r="D91" s="3">
+        <v>0</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>4</v>
@@ -9263,12 +9483,12 @@
       <c r="F91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
@@ -9276,43 +9496,43 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-600</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -9336,11 +9556,11 @@
         <v>0</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-400</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
       <c r="AG91" s="3">
         <v>0</v>
       </c>
@@ -9354,19 +9574,22 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AL91" s="3">
-        <v>-100</v>
       </c>
       <c r="AM91" s="3">
         <v>-100</v>
       </c>
       <c r="AN91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AO91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9704,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,13 +9823,16 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>4</v>
+      <c r="D94" s="3">
+        <v>0</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>4</v>
@@ -9611,12 +9840,12 @@
       <c r="F94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
         <v>0</v>
       </c>
@@ -9624,43 +9853,43 @@
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-600</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -9684,11 +9913,11 @@
         <v>0</v>
       </c>
       <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-400</v>
       </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
       <c r="AG94" s="3">
         <v>0</v>
       </c>
@@ -9702,19 +9931,22 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-300</v>
-      </c>
-      <c r="AL94" s="3">
-        <v>-100</v>
       </c>
       <c r="AM94" s="3">
         <v>-100</v>
       </c>
       <c r="AN94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AO94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,8 +9987,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9793,8 +10026,8 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9871,8 +10104,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10223,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10342,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,50 +10461,53 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E100" s="3">
         <v>5800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2300</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
+      <c r="G100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>17600</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>43800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>22500</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>9600</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
@@ -10279,20 +10524,20 @@
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>1200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>42200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>18400</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
@@ -10300,43 +10545,46 @@
         <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>9000</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
         <v>0</v>
       </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>15100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-100</v>
       </c>
-      <c r="AH100" s="3">
-        <v>0</v>
-      </c>
       <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>7200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-100</v>
       </c>
-      <c r="AK100" s="3">
-        <v>0</v>
-      </c>
       <c r="AL100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM100" s="3">
         <v>2800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>8200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10373,8 +10621,8 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10451,120 +10699,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>600</v>
+      </c>
+      <c r="E102" s="3">
         <v>1500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-9400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>8400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-14200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>30500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>13800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-5100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-6400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>38300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>15400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>6400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>12200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>4300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>5800</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-2300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CLRB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CLRB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="92">
   <si>
     <t>CLRB</t>
   </si>
@@ -656,173 +656,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -862,8 +866,8 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -940,8 +944,11 @@
       <c r="AO8" s="3">
         <v>0</v>
       </c>
+      <c r="AP8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1059,8 +1066,11 @@
       <c r="AO9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1178,8 +1188,11 @@
       <c r="AO10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1221,127 +1234,131 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E12" s="3">
         <v>3200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>7000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>4500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>4400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3900</v>
-      </c>
-      <c r="V12" s="3">
-        <v>4600</v>
       </c>
       <c r="W12" s="3">
         <v>4600</v>
       </c>
       <c r="X12" s="3">
+        <v>4600</v>
+      </c>
+      <c r="Y12" s="3">
         <v>2400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>2700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>2500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>2600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>2200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>2700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>2300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>2000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1700</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>3100</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>2300</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>2200</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>1900</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>1400</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1459,8 +1476,11 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1500,23 +1520,23 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>4</v>
@@ -1524,23 +1544,23 @@
       <c r="W14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-200</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>4</v>
+      <c r="AB14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>4</v>
@@ -1548,12 +1568,12 @@
       <c r="AE14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AF14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG14" s="3">
         <v>1700</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1572,22 +1592,25 @@
       <c r="AM14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
+      <c r="AN14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
@@ -1611,7 +1634,7 @@
         <v>100</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1697,8 +1720,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,246 +1763,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E17" s="3">
         <v>5700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2600</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-6000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-6400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-12700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-13700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-12000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-12500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-7800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-6100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-6000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-6400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-4100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2018,53 +2051,54 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
         <v>-300</v>
       </c>
       <c r="F20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G20" s="3">
         <v>-500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-10200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-12500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>15000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -2099,22 +2133,22 @@
         <v>0</v>
       </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>100</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
       <c r="AF20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG20" s="3">
         <v>100</v>
       </c>
       <c r="AH20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI20" s="3">
         <v>0</v>
@@ -2126,138 +2160,144 @@
         <v>0</v>
       </c>
       <c r="AL20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="3">
         <v>100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>100</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-5300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-5500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-6700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-14900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-26900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-17500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-10200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-7800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-6100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-5800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-6000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-6300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-2800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-3400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>-2800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2297,8 +2337,8 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2375,127 +2415,133 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-6600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-14700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-26600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-17500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-3100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2511,36 +2557,36 @@
       <c r="G24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2556,8 +2602,8 @@
       <c r="V24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
+      <c r="W24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X24" s="3">
         <v>0</v>
@@ -2613,8 +2659,11 @@
       <c r="AO24" s="3">
         <v>0</v>
       </c>
+      <c r="AP24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2732,246 +2781,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-6600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-14700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-26600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-17500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10200</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-7200</v>
       </c>
       <c r="P26" s="3">
         <v>-7200</v>
       </c>
       <c r="Q26" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="R26" s="3">
         <v>-7800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-6000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-6400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-2600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-14700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-26600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-17500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10200</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-7200</v>
       </c>
       <c r="P27" s="3">
         <v>-7200</v>
       </c>
       <c r="Q27" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="R27" s="3">
         <v>-7800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-6000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-6400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-5300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-5500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3089,8 +3147,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3208,8 +3269,11 @@
       <c r="AO29" s="3">
         <v>0</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3327,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3446,53 +3513,56 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
         <v>300</v>
       </c>
       <c r="F32" s="3">
+        <v>300</v>
+      </c>
+      <c r="G32" s="3">
         <v>500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>10200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>12500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-15000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -3527,22 +3597,22 @@
         <v>0</v>
       </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
       <c r="AF32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG32" s="3">
         <v>-100</v>
       </c>
       <c r="AH32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AI32" s="3">
         <v>0</v>
@@ -3554,138 +3624,144 @@
         <v>0</v>
       </c>
       <c r="AL32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="3">
         <v>-100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-100</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-14700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-26600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-17500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-10200</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-7200</v>
       </c>
       <c r="P33" s="3">
         <v>-7200</v>
       </c>
       <c r="Q33" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="R33" s="3">
         <v>-7800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-6000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-6400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-5300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-5500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3803,251 +3879,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-14700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-26600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-17500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-10200</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-7200</v>
       </c>
       <c r="P35" s="3">
         <v>-7200</v>
       </c>
       <c r="Q35" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="R35" s="3">
         <v>-7800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-6000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-6400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-5300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-5500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4089,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,127 +4218,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E41" s="3">
         <v>13200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>23300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>34300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>25900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>40000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>19000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>12700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>19900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>17800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>24800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>30600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>35700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>40300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>46800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>53600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>57200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>18800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>22500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>10600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>13300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>16800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>10500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>13300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>16400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>6800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>10000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>5700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>8300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>11200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>11400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4370,8 +4460,11 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4411,8 +4504,8 @@
       <c r="O43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -4489,8 +4582,11 @@
       <c r="AO43" s="3">
         <v>0</v>
       </c>
+      <c r="AP43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4530,8 +4626,8 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4608,8 +4704,11 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4649,205 +4748,211 @@
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3">
         <v>700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>300</v>
-      </c>
-      <c r="W45" s="3">
-        <v>800</v>
       </c>
       <c r="X45" s="3">
         <v>800</v>
       </c>
       <c r="Y45" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z45" s="3">
         <v>1000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>600</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>800</v>
       </c>
       <c r="AB45" s="3">
         <v>800</v>
       </c>
       <c r="AC45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AD45" s="3">
         <v>1500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>600</v>
-      </c>
-      <c r="AF45" s="3">
-        <v>700</v>
       </c>
       <c r="AG45" s="3">
         <v>700</v>
       </c>
       <c r="AH45" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="AI45" s="3">
         <v>800</v>
       </c>
       <c r="AJ45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AK45" s="3">
         <v>500</v>
-      </c>
-      <c r="AK45" s="3">
-        <v>1000</v>
       </c>
       <c r="AL45" s="3">
         <v>1000</v>
       </c>
       <c r="AM45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AN45" s="3">
         <v>900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>700</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E46" s="3">
         <v>14000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>24300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>35900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>27900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>41400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>20100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>20500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>18800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>25300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>31400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>36600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>41400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>47100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>54400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>57900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>19800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>23000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>11400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>14800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>18200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>11100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>14000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>17100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>7600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>10500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>6700</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>9300</v>
-      </c>
-      <c r="AM46" s="3">
-        <v>12200</v>
       </c>
       <c r="AN46" s="3">
         <v>12200</v>
       </c>
       <c r="AO46" s="3">
+        <v>12200</v>
+      </c>
+      <c r="AP46" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4887,8 +4992,8 @@
       <c r="O47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4965,52 +5070,55 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E48" s="3">
         <v>900</v>
-      </c>
-      <c r="E48" s="3">
-        <v>1000</v>
       </c>
       <c r="F48" s="3">
         <v>1000</v>
       </c>
       <c r="G48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H48" s="3">
         <v>1100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1200</v>
-      </c>
-      <c r="I48" s="3">
-        <v>1400</v>
       </c>
       <c r="J48" s="3">
         <v>1400</v>
       </c>
       <c r="K48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L48" s="3">
         <v>1500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1400</v>
-      </c>
-      <c r="N48" s="3">
-        <v>900</v>
       </c>
       <c r="O48" s="3">
         <v>900</v>
       </c>
       <c r="P48" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q48" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>500</v>
       </c>
       <c r="R48" s="3">
         <v>500</v>
@@ -5028,13 +5136,13 @@
         <v>500</v>
       </c>
       <c r="W48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="X48" s="3">
         <v>600</v>
       </c>
       <c r="Y48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="Z48" s="3">
         <v>700</v>
@@ -5043,22 +5151,22 @@
         <v>700</v>
       </c>
       <c r="AB48" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="AC48" s="3">
         <v>800</v>
       </c>
       <c r="AD48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AE48" s="3">
         <v>900</v>
       </c>
       <c r="AF48" s="3">
+        <v>900</v>
+      </c>
+      <c r="AG48" s="3">
         <v>500</v>
-      </c>
-      <c r="AG48" s="3">
-        <v>200</v>
       </c>
       <c r="AH48" s="3">
         <v>200</v>
@@ -5070,22 +5178,25 @@
         <v>200</v>
       </c>
       <c r="AK48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL48" s="3">
         <v>1500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1600</v>
-      </c>
-      <c r="AM48" s="3">
-        <v>1400</v>
       </c>
       <c r="AN48" s="3">
         <v>1400</v>
       </c>
       <c r="AO48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AP48" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5177,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="AG49" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="AH49" s="3">
         <v>1700</v>
@@ -5203,8 +5314,11 @@
       <c r="AO49" s="3">
         <v>1700</v>
       </c>
+      <c r="AP49" s="3">
+        <v>1700</v>
+      </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5322,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5441,8 +5558,11 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5480,7 +5600,7 @@
         <v>0</v>
       </c>
       <c r="O52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P52" s="3">
         <v>100</v>
@@ -5510,10 +5630,10 @@
         <v>100</v>
       </c>
       <c r="Y52" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z52" s="3">
         <v>200</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>100</v>
       </c>
       <c r="AA52" s="3">
         <v>100</v>
@@ -5528,26 +5648,26 @@
         <v>100</v>
       </c>
       <c r="AE52" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF52" s="3">
         <v>500</v>
-      </c>
-      <c r="AF52" s="3">
-        <v>600</v>
       </c>
       <c r="AG52" s="3">
         <v>600</v>
       </c>
       <c r="AH52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AI52" s="3">
         <v>100</v>
       </c>
-      <c r="AI52" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="3">
         <v>500</v>
       </c>
-      <c r="AK52" s="3">
-        <v>0</v>
-      </c>
       <c r="AL52" s="3">
         <v>0</v>
       </c>
@@ -5560,8 +5680,11 @@
       <c r="AO52" s="3">
         <v>0</v>
       </c>
+      <c r="AP52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5679,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E54" s="3">
         <v>15000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>25500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>37300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>29400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>42900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>21600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>19300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>25900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>32000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>37200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>42000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>47700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>55100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>58700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>20700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>23900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>8700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>15700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>19100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>12500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>15100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>19500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>7000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>9600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>12900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>9900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>12600</v>
-      </c>
-      <c r="AM54" s="3">
-        <v>15300</v>
       </c>
       <c r="AN54" s="3">
         <v>15300</v>
       </c>
       <c r="AO54" s="3">
+        <v>15300</v>
+      </c>
+      <c r="AP54" s="3">
         <v>9300</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5841,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5884,132 +6014,136 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2100</v>
-      </c>
-      <c r="AI57" s="3">
-        <v>1900</v>
       </c>
       <c r="AJ57" s="3">
         <v>1900</v>
       </c>
       <c r="AK57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AL57" s="3">
         <v>2000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
         <v>100</v>
@@ -6045,7 +6179,7 @@
         <v>100</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -6117,54 +6251,57 @@
         <v>0</v>
       </c>
       <c r="AN58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="3">
         <v>100</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>100</v>
+      </c>
+      <c r="E59" s="3">
         <v>700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>21100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8600</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P59" s="3">
-        <v>100</v>
+      <c r="P59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q59" s="3">
         <v>100</v>
@@ -6218,7 +6355,7 @@
         <v>100</v>
       </c>
       <c r="AH59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AI59" s="3">
         <v>200</v>
@@ -6227,120 +6364,123 @@
         <v>200</v>
       </c>
       <c r="AK59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AL59" s="3">
         <v>100</v>
       </c>
       <c r="AM59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AN59" s="3">
         <v>200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>100</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E60" s="3">
         <v>4700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>20300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>28600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>25400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>16500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2300</v>
-      </c>
-      <c r="AI60" s="3">
-        <v>2100</v>
       </c>
       <c r="AJ60" s="3">
         <v>2100</v>
@@ -6349,30 +6489,33 @@
         <v>2100</v>
       </c>
       <c r="AL60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AM60" s="3">
         <v>1600</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1400</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>1600</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="E61" s="3">
         <v>300</v>
       </c>
       <c r="F61" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G61" s="3">
         <v>400</v>
@@ -6384,7 +6527,7 @@
         <v>400</v>
       </c>
       <c r="J61" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K61" s="3">
         <v>500</v>
@@ -6402,7 +6545,7 @@
         <v>500</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
@@ -6429,13 +6572,13 @@
         <v>0</v>
       </c>
       <c r="Y61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Z61" s="3">
         <v>200</v>
       </c>
       <c r="AA61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB61" s="3">
         <v>0</v>
@@ -6479,8 +6622,11 @@
       <c r="AO61" s="3">
         <v>0</v>
       </c>
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6520,11 +6666,11 @@
       <c r="O62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q62" s="3">
         <v>600</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>100</v>
       </c>
       <c r="R62" s="3">
         <v>100</v>
@@ -6533,7 +6679,7 @@
         <v>100</v>
       </c>
       <c r="T62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U62" s="3">
         <v>200</v>
@@ -6542,7 +6688,7 @@
         <v>200</v>
       </c>
       <c r="W62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X62" s="3">
         <v>300</v>
@@ -6551,7 +6697,7 @@
         <v>300</v>
       </c>
       <c r="Z62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AA62" s="3">
         <v>400</v>
@@ -6563,28 +6709,28 @@
         <v>400</v>
       </c>
       <c r="AD62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AE62" s="3">
         <v>500</v>
       </c>
       <c r="AF62" s="3">
+        <v>500</v>
+      </c>
+      <c r="AG62" s="3">
         <v>200</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AI62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ62" s="3">
-        <v>0</v>
+      <c r="AJ62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AL62" s="3">
         <v>100</v>
@@ -6598,8 +6744,11 @@
       <c r="AO62" s="3">
         <v>100</v>
       </c>
+      <c r="AP62" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6717,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6836,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6955,127 +7110,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E66" s="3">
         <v>5100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>20700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>29000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>25900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>17000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2300</v>
-      </c>
-      <c r="AI66" s="3">
-        <v>2100</v>
       </c>
       <c r="AJ66" s="3">
         <v>2100</v>
       </c>
       <c r="AK66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AL66" s="3">
         <v>2300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1800</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7117,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7236,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7355,8 +7520,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7376,22 +7544,22 @@
         <v>1900</v>
       </c>
       <c r="I70" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J70" s="3">
         <v>15000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>9200</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>18400</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>6100</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>19300</v>
-      </c>
-      <c r="N70" s="3">
-        <v>1400</v>
       </c>
       <c r="O70" s="3">
         <v>1400</v>
@@ -7415,16 +7583,16 @@
         <v>1400</v>
       </c>
       <c r="V70" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W70" s="3">
         <v>8600</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>11700</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>20000</v>
-      </c>
-      <c r="Y70" s="3">
-        <v>1100</v>
       </c>
       <c r="Z70" s="3">
         <v>1100</v>
@@ -7442,26 +7610,26 @@
         <v>1100</v>
       </c>
       <c r="AE70" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AF70" s="3">
         <v>1800</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>2500</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>3500</v>
       </c>
-      <c r="AH70" s="3">
-        <v>0</v>
-      </c>
       <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="3">
         <v>600</v>
       </c>
-      <c r="AJ70" s="3">
+      <c r="AK70" s="3">
         <v>1000</v>
       </c>
-      <c r="AK70" s="3">
-        <v>0</v>
-      </c>
       <c r="AL70" s="3">
         <v>0</v>
       </c>
@@ -7469,13 +7637,16 @@
         <v>0</v>
       </c>
       <c r="AN70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="3">
         <v>900</v>
       </c>
-      <c r="AO70" s="3">
+      <c r="AP70" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7593,127 +7764,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-274800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-269100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-263800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-259400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-253900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-247300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-245000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-230300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-229400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-202800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-210000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-196300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-188100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-179500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-172300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-164500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-157000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-150900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-145000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-139200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-133100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-126800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-123200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-119300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-115600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-111700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-108300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-104400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-101200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-97600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-93800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-90700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-87800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-84300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-80300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-76800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-73700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-70800</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-68200</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7831,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7950,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8069,127 +8252,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E76" s="3">
         <v>8000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-4600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-19800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-14700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-1800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>18800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>25800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>31700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>37200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>35300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>38000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>34800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>15100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>18800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>11100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>8100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>10700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>13400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>9800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>7600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>10900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>13700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>12700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8307,251 +8496,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-14700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-26600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-17500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-10200</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-7200</v>
       </c>
       <c r="P81" s="3">
         <v>-7200</v>
       </c>
       <c r="Q81" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="R81" s="3">
         <v>-7800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-6000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-6400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-5300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-5500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8593,8 +8791,9 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8614,7 +8813,7 @@
         <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
         <v>0</v>
@@ -8695,10 +8894,10 @@
         <v>0</v>
       </c>
       <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK83" s="3">
         <v>1300</v>
-      </c>
-      <c r="AK83" s="3">
-        <v>100</v>
       </c>
       <c r="AL83" s="3">
         <v>100</v>
@@ -8712,8 +8911,11 @@
       <c r="AO83" s="3">
         <v>100</v>
       </c>
+      <c r="AP83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8950,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9069,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9188,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9307,127 +9521,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-4300</v>
+        <v>-4800</v>
       </c>
       <c r="E89" s="3">
         <v>-4300</v>
       </c>
       <c r="F89" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="G89" s="3">
         <v>-5100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-10900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-9200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-13400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-9600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-8100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-7000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-5800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-5000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-6400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-6900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-4800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-3200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9469,16 +9689,17 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
         <v>0</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>4</v>
+      <c r="E91" s="3">
+        <v>0</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>4</v>
@@ -9486,12 +9707,12 @@
       <c r="G91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
@@ -9499,43 +9720,43 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-600</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -9559,11 +9780,11 @@
         <v>0</v>
       </c>
       <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-400</v>
       </c>
-      <c r="AG91" s="3">
-        <v>0</v>
-      </c>
       <c r="AH91" s="3">
         <v>0</v>
       </c>
@@ -9577,19 +9798,22 @@
         <v>0</v>
       </c>
       <c r="AL91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AM91" s="3">
-        <v>-100</v>
       </c>
       <c r="AN91" s="3">
         <v>-100</v>
       </c>
       <c r="AO91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AP91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9707,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9826,16 +10053,19 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
         <v>0</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>4</v>
+      <c r="E94" s="3">
+        <v>0</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>4</v>
@@ -9843,12 +10073,12 @@
       <c r="G94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
@@ -9856,43 +10086,43 @@
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-600</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>4</v>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="X94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
@@ -9916,11 +10146,11 @@
         <v>0</v>
       </c>
       <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-400</v>
       </c>
-      <c r="AG94" s="3">
-        <v>0</v>
-      </c>
       <c r="AH94" s="3">
         <v>0</v>
       </c>
@@ -9934,19 +10164,22 @@
         <v>0</v>
       </c>
       <c r="AL94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM94" s="3">
         <v>-300</v>
-      </c>
-      <c r="AM94" s="3">
-        <v>-100</v>
       </c>
       <c r="AN94" s="3">
         <v>-100</v>
       </c>
       <c r="AO94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AP94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9988,8 +10221,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10029,8 +10263,8 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10107,8 +10341,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10226,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10345,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10464,53 +10707,56 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E100" s="3">
         <v>5000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2300</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
+      <c r="H100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>17600</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>43800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>22500</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>9600</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
@@ -10527,20 +10773,20 @@
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>1200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>42200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>18400</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
@@ -10548,43 +10794,46 @@
         <v>0</v>
       </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>9000</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
         <v>0</v>
       </c>
       <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>15100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-100</v>
       </c>
-      <c r="AI100" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK100" s="3">
         <v>7200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-100</v>
       </c>
-      <c r="AL100" s="3">
-        <v>0</v>
-      </c>
       <c r="AM100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN100" s="3">
         <v>2800</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>8200</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10624,8 +10873,8 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10702,123 +10951,129 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E102" s="3">
         <v>600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>8400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-14200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>30500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>13800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-7000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-5800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-5100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-6800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>38300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>15400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>6400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>12200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>4300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>5800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-2300</v>
       </c>
     </row>
